--- a/OV_F407VGT6_2026.01.18/天空星引脚配置.xlsx
+++ b/OV_F407VGT6_2026.01.18/天空星引脚配置.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="G:\Oscillatory_Viscometer\OV_F407VGT6_2026.01.18\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{23C0AD97-711F-4E47-99F6-D13DB1C838AD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{83E90E75-2293-4DA1-8E39-86450A9419A6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-28920" yWindow="-105" windowWidth="29040" windowHeight="16440" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -304,23 +304,23 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>OLED显示</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>扫频控制</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>按键扫描+高频PWM输入</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>准备挪到PA15</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
     <t>准备挪到PA8</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>高频PWM输入</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>OLED显示（100ms）+按键扫描（5ms）</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -602,10 +602,10 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="11" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -903,7 +903,7 @@
     <col min="11" max="11" width="9.25" style="1" bestFit="1" customWidth="1"/>
     <col min="12" max="12" width="15" style="1" bestFit="1" customWidth="1"/>
     <col min="13" max="14" width="7.75" style="1" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="23.5" style="1" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="37.5" style="1" bestFit="1" customWidth="1"/>
     <col min="16" max="16384" width="9" style="1"/>
   </cols>
   <sheetData>
@@ -952,7 +952,7 @@
       </c>
     </row>
     <row r="2" spans="1:15" x14ac:dyDescent="0.2">
-      <c r="A2" s="23" t="s">
+      <c r="A2" s="24" t="s">
         <v>0</v>
       </c>
       <c r="B2" s="3">
@@ -961,7 +961,7 @@
       <c r="C2" s="6" t="s">
         <v>4</v>
       </c>
-      <c r="D2" s="24"/>
+      <c r="D2" s="23"/>
       <c r="F2" s="10" t="s">
         <v>49</v>
       </c>
@@ -1006,11 +1006,11 @@
       </c>
     </row>
     <row r="3" spans="1:15" x14ac:dyDescent="0.2">
-      <c r="A3" s="23"/>
+      <c r="A3" s="24"/>
       <c r="B3" s="3">
         <v>1</v>
       </c>
-      <c r="C3" s="24"/>
+      <c r="C3" s="23"/>
       <c r="D3" s="6" t="s">
         <v>48</v>
       </c>
@@ -1054,15 +1054,15 @@
         <v>200. µs</v>
       </c>
       <c r="O3" s="21" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
     </row>
     <row r="4" spans="1:15" x14ac:dyDescent="0.2">
-      <c r="A4" s="23"/>
+      <c r="A4" s="24"/>
       <c r="B4" s="3">
         <v>2</v>
       </c>
-      <c r="C4" s="24"/>
+      <c r="C4" s="23"/>
       <c r="D4" s="8" t="s">
         <v>43</v>
       </c>
@@ -1084,29 +1084,33 @@
         <v>100. ms</v>
       </c>
       <c r="K4" s="14">
-        <v>16800</v>
+        <v>672</v>
       </c>
       <c r="L4" s="15">
-        <v>1000</v>
+        <v>50</v>
       </c>
       <c r="M4" s="15">
-        <f t="shared" si="2"/>
-        <v>10</v>
+        <f t="shared" ref="M4" si="4">$M$1/(K4*L4)</f>
+        <v>5000</v>
       </c>
       <c r="N4" s="16" t="str">
-        <f t="shared" si="3"/>
-        <v>100. ms</v>
+        <f t="shared" ref="N4" si="5">_xlfn.LET(_xlpm.t,1/M4,
+ IF(_xlpm.t&lt;0.000001, TEXT(_xlpm.t*1000000000,"0.###")&amp;" ns",
+ IF(_xlpm.t&lt;0.001, TEXT(_xlpm.t*1000000,"0.###")&amp;" µs",
+ IF(_xlpm.t&lt;1,    TEXT(_xlpm.t*1000,"0.###")&amp;" ms",
+           TEXT(_xlpm.t,"0.###")&amp;" s"))))</f>
+        <v>200. µs</v>
       </c>
       <c r="O4" s="21" t="s">
-        <v>69</v>
+        <v>73</v>
       </c>
     </row>
     <row r="5" spans="1:15" x14ac:dyDescent="0.2">
-      <c r="A5" s="23"/>
+      <c r="A5" s="24"/>
       <c r="B5" s="3">
         <v>3</v>
       </c>
-      <c r="C5" s="24"/>
+      <c r="C5" s="23"/>
       <c r="D5" s="8" t="s">
         <v>44</v>
       </c>
@@ -1142,11 +1146,11 @@
         <v>1. ms</v>
       </c>
       <c r="O5" s="21" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
     </row>
     <row r="6" spans="1:15" x14ac:dyDescent="0.2">
-      <c r="A6" s="23"/>
+      <c r="A6" s="24"/>
       <c r="B6" s="3">
         <v>4</v>
       </c>
@@ -1157,7 +1161,7 @@
         <v>45</v>
       </c>
       <c r="E6" s="1" t="s">
-        <v>73</v>
+        <v>71</v>
       </c>
       <c r="F6" s="14" t="s">
         <v>53</v>
@@ -1183,7 +1187,7 @@
       <c r="O6" s="21"/>
     </row>
     <row r="7" spans="1:15" x14ac:dyDescent="0.2">
-      <c r="A7" s="23"/>
+      <c r="A7" s="24"/>
       <c r="B7" s="3">
         <v>5</v>
       </c>
@@ -1194,7 +1198,7 @@
         <v>47</v>
       </c>
       <c r="E7" s="1" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="F7" s="14" t="s">
         <v>54</v>
@@ -1220,7 +1224,7 @@
       <c r="O7" s="21"/>
     </row>
     <row r="8" spans="1:15" x14ac:dyDescent="0.2">
-      <c r="A8" s="23"/>
+      <c r="A8" s="24"/>
       <c r="B8" s="3">
         <v>6</v>
       </c>
@@ -1252,7 +1256,7 @@
       <c r="O8" s="21"/>
     </row>
     <row r="9" spans="1:15" x14ac:dyDescent="0.2">
-      <c r="A9" s="23"/>
+      <c r="A9" s="24"/>
       <c r="B9" s="3">
         <v>7</v>
       </c>
@@ -1284,7 +1288,7 @@
       <c r="O9" s="21"/>
     </row>
     <row r="10" spans="1:15" x14ac:dyDescent="0.2">
-      <c r="A10" s="23"/>
+      <c r="A10" s="24"/>
       <c r="B10" s="3">
         <v>8</v>
       </c>
@@ -1313,7 +1317,7 @@
       <c r="O10" s="21"/>
     </row>
     <row r="11" spans="1:15" x14ac:dyDescent="0.2">
-      <c r="A11" s="23"/>
+      <c r="A11" s="24"/>
       <c r="B11" s="2">
         <v>9</v>
       </c>
@@ -1345,7 +1349,7 @@
       <c r="O11" s="21"/>
     </row>
     <row r="12" spans="1:15" x14ac:dyDescent="0.2">
-      <c r="A12" s="23"/>
+      <c r="A12" s="24"/>
       <c r="B12" s="2">
         <v>10</v>
       </c>
@@ -1377,7 +1381,7 @@
       <c r="O12" s="21"/>
     </row>
     <row r="13" spans="1:15" x14ac:dyDescent="0.2">
-      <c r="A13" s="23"/>
+      <c r="A13" s="24"/>
       <c r="B13" s="2">
         <v>11</v>
       </c>
@@ -1409,7 +1413,7 @@
       <c r="O13" s="21"/>
     </row>
     <row r="14" spans="1:15" x14ac:dyDescent="0.2">
-      <c r="A14" s="23"/>
+      <c r="A14" s="24"/>
       <c r="B14" s="2">
         <v>12</v>
       </c>
@@ -1441,14 +1445,14 @@
       <c r="O14" s="21"/>
     </row>
     <row r="15" spans="1:15" x14ac:dyDescent="0.2">
-      <c r="A15" s="23"/>
+      <c r="A15" s="24"/>
       <c r="B15" s="2">
         <v>13</v>
       </c>
       <c r="C15" s="6" t="s">
         <v>19</v>
       </c>
-      <c r="D15" s="24"/>
+      <c r="D15" s="23"/>
       <c r="F15" s="17" t="s">
         <v>62</v>
       </c>
@@ -1475,17 +1479,17 @@
       <c r="O15" s="22"/>
     </row>
     <row r="16" spans="1:15" x14ac:dyDescent="0.2">
-      <c r="A16" s="23"/>
+      <c r="A16" s="24"/>
       <c r="B16" s="2">
         <v>14</v>
       </c>
       <c r="C16" s="8" t="s">
         <v>20</v>
       </c>
-      <c r="D16" s="24"/>
+      <c r="D16" s="23"/>
     </row>
     <row r="17" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A17" s="23"/>
+      <c r="A17" s="24"/>
       <c r="B17" s="3">
         <v>15</v>
       </c>
@@ -1493,7 +1497,7 @@
       <c r="D17" s="2"/>
     </row>
     <row r="18" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A18" s="23" t="s">
+      <c r="A18" s="24" t="s">
         <v>1</v>
       </c>
       <c r="B18" s="3">
@@ -1503,7 +1507,7 @@
       <c r="D18" s="2"/>
     </row>
     <row r="19" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A19" s="23"/>
+      <c r="A19" s="24"/>
       <c r="B19" s="3">
         <v>1</v>
       </c>
@@ -1511,17 +1515,17 @@
       <c r="D19" s="2"/>
     </row>
     <row r="20" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A20" s="23"/>
+      <c r="A20" s="24"/>
       <c r="B20" s="2">
         <v>2</v>
       </c>
       <c r="C20" s="6" t="s">
         <v>46</v>
       </c>
-      <c r="D20" s="24"/>
+      <c r="D20" s="23"/>
     </row>
     <row r="21" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A21" s="23"/>
+      <c r="A21" s="24"/>
       <c r="B21" s="2">
         <v>3</v>
       </c>
@@ -1531,7 +1535,7 @@
       <c r="D21" s="2"/>
     </row>
     <row r="22" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A22" s="23"/>
+      <c r="A22" s="24"/>
       <c r="B22" s="3">
         <v>4</v>
       </c>
@@ -1539,7 +1543,7 @@
       <c r="D22" s="2"/>
     </row>
     <row r="23" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A23" s="23"/>
+      <c r="A23" s="24"/>
       <c r="B23" s="3">
         <v>5</v>
       </c>
@@ -1547,103 +1551,103 @@
       <c r="D23" s="2"/>
     </row>
     <row r="24" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A24" s="23"/>
+      <c r="A24" s="24"/>
       <c r="B24" s="3">
         <v>6</v>
       </c>
-      <c r="C24" s="24"/>
-      <c r="D24" s="24" t="s">
+      <c r="C24" s="23"/>
+      <c r="D24" s="6" t="s">
         <v>36</v>
       </c>
     </row>
     <row r="25" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A25" s="23"/>
+      <c r="A25" s="24"/>
       <c r="B25" s="3">
         <v>7</v>
       </c>
-      <c r="C25" s="24"/>
-      <c r="D25" s="24" t="s">
+      <c r="C25" s="23"/>
+      <c r="D25" s="8" t="s">
         <v>37</v>
       </c>
     </row>
     <row r="26" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A26" s="23"/>
+      <c r="A26" s="24"/>
       <c r="B26" s="3">
         <v>8</v>
       </c>
-      <c r="C26" s="24"/>
-      <c r="D26" s="24"/>
+      <c r="C26" s="23"/>
+      <c r="D26" s="8"/>
     </row>
     <row r="27" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A27" s="23"/>
+      <c r="A27" s="24"/>
       <c r="B27" s="3">
         <v>9</v>
       </c>
-      <c r="C27" s="24"/>
-      <c r="D27" s="24"/>
+      <c r="C27" s="23"/>
+      <c r="D27" s="8"/>
     </row>
     <row r="28" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A28" s="23"/>
+      <c r="A28" s="24"/>
       <c r="B28" s="3">
         <v>10</v>
       </c>
-      <c r="C28" s="24"/>
-      <c r="D28" s="24" t="s">
+      <c r="C28" s="23"/>
+      <c r="D28" s="8" t="s">
         <v>41</v>
       </c>
     </row>
     <row r="29" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A29" s="23"/>
+      <c r="A29" s="24"/>
       <c r="B29" s="3">
         <v>11</v>
       </c>
-      <c r="C29" s="24"/>
-      <c r="D29" s="24" t="s">
+      <c r="C29" s="23"/>
+      <c r="D29" s="8" t="s">
         <v>42</v>
       </c>
     </row>
     <row r="30" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A30" s="23"/>
+      <c r="A30" s="24"/>
       <c r="B30" s="3">
         <v>12</v>
       </c>
-      <c r="C30" s="24"/>
-      <c r="D30" s="24" t="s">
+      <c r="C30" s="23"/>
+      <c r="D30" s="8" t="s">
         <v>35</v>
       </c>
     </row>
     <row r="31" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A31" s="23"/>
+      <c r="A31" s="24"/>
       <c r="B31" s="3">
         <v>13</v>
       </c>
-      <c r="C31" s="24"/>
-      <c r="D31" s="24" t="s">
+      <c r="C31" s="23"/>
+      <c r="D31" s="8" t="s">
         <v>38</v>
       </c>
     </row>
     <row r="32" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A32" s="23"/>
+      <c r="A32" s="24"/>
       <c r="B32" s="3">
         <v>14</v>
       </c>
-      <c r="C32" s="24"/>
-      <c r="D32" s="24" t="s">
+      <c r="C32" s="23"/>
+      <c r="D32" s="8" t="s">
         <v>39</v>
       </c>
     </row>
     <row r="33" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A33" s="23"/>
+      <c r="A33" s="24"/>
       <c r="B33" s="3">
         <v>15</v>
       </c>
-      <c r="C33" s="24"/>
-      <c r="D33" s="24" t="s">
+      <c r="C33" s="23"/>
+      <c r="D33" s="8" t="s">
         <v>40</v>
       </c>
     </row>
     <row r="34" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A34" s="23" t="s">
+      <c r="A34" s="24" t="s">
         <v>2</v>
       </c>
       <c r="B34" s="3">
@@ -1653,7 +1657,7 @@
       <c r="D34" s="2"/>
     </row>
     <row r="35" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A35" s="23"/>
+      <c r="A35" s="24"/>
       <c r="B35" s="3">
         <v>1</v>
       </c>
@@ -1661,7 +1665,7 @@
       <c r="D35" s="2"/>
     </row>
     <row r="36" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A36" s="23"/>
+      <c r="A36" s="24"/>
       <c r="B36" s="3">
         <v>2</v>
       </c>
@@ -1669,7 +1673,7 @@
       <c r="D36" s="2"/>
     </row>
     <row r="37" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A37" s="23"/>
+      <c r="A37" s="24"/>
       <c r="B37" s="3">
         <v>3</v>
       </c>
@@ -1677,7 +1681,7 @@
       <c r="D37" s="2"/>
     </row>
     <row r="38" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A38" s="23"/>
+      <c r="A38" s="24"/>
       <c r="B38" s="3">
         <v>4</v>
       </c>
@@ -1685,7 +1689,7 @@
       <c r="D38" s="2"/>
     </row>
     <row r="39" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A39" s="23"/>
+      <c r="A39" s="24"/>
       <c r="B39" s="3">
         <v>5</v>
       </c>
@@ -1693,7 +1697,7 @@
       <c r="D39" s="2"/>
     </row>
     <row r="40" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A40" s="23"/>
+      <c r="A40" s="24"/>
       <c r="B40" s="3">
         <v>6</v>
       </c>
@@ -1701,7 +1705,7 @@
       <c r="D40" s="2"/>
     </row>
     <row r="41" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A41" s="23"/>
+      <c r="A41" s="24"/>
       <c r="B41" s="3">
         <v>7</v>
       </c>
@@ -1709,7 +1713,7 @@
       <c r="D41" s="2"/>
     </row>
     <row r="42" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A42" s="23"/>
+      <c r="A42" s="24"/>
       <c r="B42" s="3">
         <v>8</v>
       </c>
@@ -1719,7 +1723,7 @@
       <c r="D42" s="2"/>
     </row>
     <row r="43" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A43" s="23"/>
+      <c r="A43" s="24"/>
       <c r="B43" s="3">
         <v>9</v>
       </c>
@@ -1729,7 +1733,7 @@
       <c r="D43" s="2"/>
     </row>
     <row r="44" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A44" s="23"/>
+      <c r="A44" s="24"/>
       <c r="B44" s="3">
         <v>10</v>
       </c>
@@ -1739,7 +1743,7 @@
       <c r="D44" s="2"/>
     </row>
     <row r="45" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A45" s="23"/>
+      <c r="A45" s="24"/>
       <c r="B45" s="3">
         <v>11</v>
       </c>
@@ -1749,7 +1753,7 @@
       <c r="D45" s="2"/>
     </row>
     <row r="46" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A46" s="23"/>
+      <c r="A46" s="24"/>
       <c r="B46" s="3">
         <v>12</v>
       </c>
@@ -1759,7 +1763,7 @@
       <c r="D46" s="2"/>
     </row>
     <row r="47" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A47" s="23"/>
+      <c r="A47" s="24"/>
       <c r="B47" s="3">
         <v>13</v>
       </c>
@@ -1767,7 +1771,7 @@
       <c r="D47" s="2"/>
     </row>
     <row r="48" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A48" s="23"/>
+      <c r="A48" s="24"/>
       <c r="B48" s="2">
         <v>14</v>
       </c>
@@ -1777,7 +1781,7 @@
       <c r="D48" s="8"/>
     </row>
     <row r="49" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A49" s="23"/>
+      <c r="A49" s="24"/>
       <c r="B49" s="2">
         <v>15</v>
       </c>
@@ -1787,7 +1791,7 @@
       <c r="D49" s="8"/>
     </row>
     <row r="50" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A50" s="23" t="s">
+      <c r="A50" s="24" t="s">
         <v>3</v>
       </c>
       <c r="B50" s="3">
@@ -1799,7 +1803,7 @@
       </c>
     </row>
     <row r="51" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A51" s="23"/>
+      <c r="A51" s="24"/>
       <c r="B51" s="3">
         <v>1</v>
       </c>
@@ -1809,7 +1813,7 @@
       </c>
     </row>
     <row r="52" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A52" s="23"/>
+      <c r="A52" s="24"/>
       <c r="B52" s="3">
         <v>2</v>
       </c>
@@ -1819,7 +1823,7 @@
       <c r="D52" s="2"/>
     </row>
     <row r="53" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A53" s="23"/>
+      <c r="A53" s="24"/>
       <c r="B53" s="3">
         <v>3</v>
       </c>
@@ -1829,7 +1833,7 @@
       <c r="D53" s="2"/>
     </row>
     <row r="54" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A54" s="23"/>
+      <c r="A54" s="24"/>
       <c r="B54" s="3">
         <v>4</v>
       </c>
@@ -1837,7 +1841,7 @@
       <c r="D54" s="2"/>
     </row>
     <row r="55" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A55" s="23"/>
+      <c r="A55" s="24"/>
       <c r="B55" s="3">
         <v>5</v>
       </c>
@@ -1845,7 +1849,7 @@
       <c r="D55" s="2"/>
     </row>
     <row r="56" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A56" s="23"/>
+      <c r="A56" s="24"/>
       <c r="B56" s="3">
         <v>6</v>
       </c>
@@ -1853,7 +1857,7 @@
       <c r="D56" s="2"/>
     </row>
     <row r="57" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A57" s="23"/>
+      <c r="A57" s="24"/>
       <c r="B57" s="3">
         <v>7</v>
       </c>
@@ -1861,7 +1865,7 @@
       <c r="D57" s="2"/>
     </row>
     <row r="58" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A58" s="23"/>
+      <c r="A58" s="24"/>
       <c r="B58" s="3">
         <v>8</v>
       </c>
@@ -1869,7 +1873,7 @@
       <c r="D58" s="2"/>
     </row>
     <row r="59" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A59" s="23"/>
+      <c r="A59" s="24"/>
       <c r="B59" s="3">
         <v>9</v>
       </c>
@@ -1877,7 +1881,7 @@
       <c r="D59" s="2"/>
     </row>
     <row r="60" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A60" s="23"/>
+      <c r="A60" s="24"/>
       <c r="B60" s="3">
         <v>10</v>
       </c>
@@ -1885,7 +1889,7 @@
       <c r="D60" s="2"/>
     </row>
     <row r="61" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A61" s="23"/>
+      <c r="A61" s="24"/>
       <c r="B61" s="3">
         <v>11</v>
       </c>
@@ -1893,7 +1897,7 @@
       <c r="D61" s="2"/>
     </row>
     <row r="62" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A62" s="23"/>
+      <c r="A62" s="24"/>
       <c r="B62" s="3">
         <v>12</v>
       </c>
@@ -1901,7 +1905,7 @@
       <c r="D62" s="2"/>
     </row>
     <row r="63" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A63" s="23"/>
+      <c r="A63" s="24"/>
       <c r="B63" s="3">
         <v>13</v>
       </c>
@@ -1909,7 +1913,7 @@
       <c r="D63" s="2"/>
     </row>
     <row r="64" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A64" s="23"/>
+      <c r="A64" s="24"/>
       <c r="B64" s="3">
         <v>14</v>
       </c>
@@ -1917,7 +1921,7 @@
       <c r="D64" s="2"/>
     </row>
     <row r="65" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A65" s="23"/>
+      <c r="A65" s="24"/>
       <c r="B65" s="3">
         <v>15</v>
       </c>
@@ -1925,7 +1929,7 @@
       <c r="D65" s="2"/>
     </row>
     <row r="66" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A66" s="23" t="s">
+      <c r="A66" s="24" t="s">
         <v>8</v>
       </c>
       <c r="B66" s="3">
@@ -1935,7 +1939,7 @@
       <c r="D66" s="2"/>
     </row>
     <row r="67" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A67" s="23"/>
+      <c r="A67" s="24"/>
       <c r="B67" s="3">
         <v>1</v>
       </c>
@@ -1943,7 +1947,7 @@
       <c r="D67" s="2"/>
     </row>
     <row r="68" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A68" s="23"/>
+      <c r="A68" s="24"/>
       <c r="B68" s="3">
         <v>2</v>
       </c>
@@ -1951,7 +1955,7 @@
       <c r="D68" s="2"/>
     </row>
     <row r="69" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A69" s="23"/>
+      <c r="A69" s="24"/>
       <c r="B69" s="3">
         <v>3</v>
       </c>
@@ -1959,7 +1963,7 @@
       <c r="D69" s="2"/>
     </row>
     <row r="70" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A70" s="23"/>
+      <c r="A70" s="24"/>
       <c r="B70" s="3">
         <v>4</v>
       </c>
@@ -1967,7 +1971,7 @@
       <c r="D70" s="2"/>
     </row>
     <row r="71" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A71" s="23"/>
+      <c r="A71" s="24"/>
       <c r="B71" s="3">
         <v>5</v>
       </c>
@@ -1975,7 +1979,7 @@
       <c r="D71" s="2"/>
     </row>
     <row r="72" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A72" s="23"/>
+      <c r="A72" s="24"/>
       <c r="B72" s="3">
         <v>6</v>
       </c>
@@ -1983,7 +1987,7 @@
       <c r="D72" s="2"/>
     </row>
     <row r="73" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A73" s="23"/>
+      <c r="A73" s="24"/>
       <c r="B73" s="3">
         <v>7</v>
       </c>
@@ -1991,7 +1995,7 @@
       <c r="D73" s="2"/>
     </row>
     <row r="74" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A74" s="23"/>
+      <c r="A74" s="24"/>
       <c r="B74" s="3">
         <v>8</v>
       </c>
@@ -1999,7 +2003,7 @@
       <c r="D74" s="2"/>
     </row>
     <row r="75" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A75" s="23"/>
+      <c r="A75" s="24"/>
       <c r="B75" s="3">
         <v>9</v>
       </c>
@@ -2007,7 +2011,7 @@
       <c r="D75" s="2"/>
     </row>
     <row r="76" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A76" s="23"/>
+      <c r="A76" s="24"/>
       <c r="B76" s="3">
         <v>10</v>
       </c>
@@ -2015,7 +2019,7 @@
       <c r="D76" s="2"/>
     </row>
     <row r="77" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A77" s="23"/>
+      <c r="A77" s="24"/>
       <c r="B77" s="3">
         <v>11</v>
       </c>
@@ -2023,7 +2027,7 @@
       <c r="D77" s="2"/>
     </row>
     <row r="78" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A78" s="23"/>
+      <c r="A78" s="24"/>
       <c r="B78" s="3">
         <v>12</v>
       </c>
@@ -2031,7 +2035,7 @@
       <c r="D78" s="2"/>
     </row>
     <row r="79" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A79" s="23"/>
+      <c r="A79" s="24"/>
       <c r="B79" s="3">
         <v>13</v>
       </c>
@@ -2039,7 +2043,7 @@
       <c r="D79" s="2"/>
     </row>
     <row r="80" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A80" s="23"/>
+      <c r="A80" s="24"/>
       <c r="B80" s="3">
         <v>14</v>
       </c>
@@ -2047,7 +2051,7 @@
       <c r="D80" s="2"/>
     </row>
     <row r="81" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A81" s="23"/>
+      <c r="A81" s="24"/>
       <c r="B81" s="3">
         <v>15</v>
       </c>
@@ -2055,7 +2059,7 @@
       <c r="D81" s="2"/>
     </row>
     <row r="82" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A82" s="23" t="s">
+      <c r="A82" s="24" t="s">
         <v>10</v>
       </c>
       <c r="B82" s="2">
@@ -2064,17 +2068,17 @@
       <c r="C82" s="6" t="s">
         <v>11</v>
       </c>
-      <c r="D82" s="24"/>
+      <c r="D82" s="23"/>
     </row>
     <row r="83" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A83" s="23"/>
+      <c r="A83" s="24"/>
       <c r="B83" s="2">
         <v>1</v>
       </c>
       <c r="C83" s="6" t="s">
         <v>12</v>
       </c>
-      <c r="D83" s="24"/>
+      <c r="D83" s="23"/>
     </row>
   </sheetData>
   <mergeCells count="6">

--- a/OV_F407VGT6_2026.01.18/天空星引脚配置.xlsx
+++ b/OV_F407VGT6_2026.01.18/天空星引脚配置.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29530"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29628"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="G:\Oscillatory_Viscometer\OV_F407VGT6_2026.01.18\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{83E90E75-2293-4DA1-8E39-86450A9419A6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BB72E904-2A4D-4036-A7D1-B19B71D34DFA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>

--- a/OV_F407VGT6_2026.01.18/天空星引脚配置.xlsx
+++ b/OV_F407VGT6_2026.01.18/天空星引脚配置.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29628"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29530"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="G:\Oscillatory_Viscometer\OV_F407VGT6_2026.01.18\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BB72E904-2A4D-4036-A7D1-B19B71D34DFA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{83E90E75-2293-4DA1-8E39-86450A9419A6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>

--- a/OV_F407VGT6_2026.01.18/天空星引脚配置.xlsx
+++ b/OV_F407VGT6_2026.01.18/天空星引脚配置.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29530"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29822"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="G:\Oscillatory_Viscometer\OV_F407VGT6_2026.01.18\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{83E90E75-2293-4DA1-8E39-86450A9419A6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{21628AEF-5724-4F8A-B286-D625F9143E5E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="77" uniqueCount="74">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="97" uniqueCount="81">
   <si>
     <t>A</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -250,77 +250,115 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
+    <t>Prescaler</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Counter Period</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Timer</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>时间</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>功能</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>振动频率控制</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>扫频控制</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>高频PWM输入</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>OLED显示（100ms）+按键扫描（5ms）</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>ADC采样速率控制</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>ADC</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Clock</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Bus</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>APB2</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>APB1</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>频率</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>TIM8</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>TIM9</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>TIM10</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>TIM11</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
     <t>TIM5</t>
+    <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
     <t>TIM6</t>
+    <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
     <t>TIM7</t>
-  </si>
-  <si>
-    <t>TIM8</t>
-  </si>
-  <si>
-    <t>TIM9</t>
-  </si>
-  <si>
-    <t>TIM10</t>
-  </si>
-  <si>
-    <t>TIM11</t>
+    <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
     <t>TIM12</t>
+    <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
     <t>TIM13</t>
+    <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
     <t>TIM14</t>
-  </si>
-  <si>
-    <t>Prescaler</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>Counter Period</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>Timer</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>时间</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>功能</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>振动频率控制</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>扫频控制</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>准备挪到PA15</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>准备挪到PA8</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>高频PWM输入</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>OLED显示（100ms）+按键扫描（5ms）</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>F103C8T6</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>F407VGT6</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -328,8 +366,9 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <numFmts count="1">
+  <numFmts count="2">
     <numFmt numFmtId="176" formatCode="[&gt;=1000000]0.##,,&quot;M&quot;;[&gt;=1000]0.##,&quot;k&quot;;0"/>
+    <numFmt numFmtId="180" formatCode="0_);[Red]\(0\)"/>
   </numFmts>
   <fonts count="5" x14ac:knownFonts="1">
     <font>
@@ -371,7 +410,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="6">
+  <fills count="10">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -402,8 +441,32 @@
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.79998168889431442"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.59999389629810485"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.39997558519241921"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="12">
+  <borders count="15">
     <border>
       <left/>
       <right/>
@@ -530,11 +593,48 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="25">
+  <cellXfs count="45">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -563,9 +663,6 @@
     <xf numFmtId="176" fontId="3" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -575,18 +672,12 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="176" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -606,6 +697,75 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="180" fontId="0" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="180" fontId="0" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="180" fontId="0" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="10" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="7" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="6" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="7" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="176" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="7" borderId="10" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="7" borderId="11" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="4" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="6" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="12" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="9" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="9" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="9" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="8" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="8" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="8" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -888,7 +1048,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:O83"/>
+  <dimension ref="A1:Q83"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="6.125" style="1" bestFit="1" customWidth="1"/>
@@ -896,18 +1056,20 @@
     <col min="3" max="3" width="14.375" style="1" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="14.75" style="1" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="13.625" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="6.625" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="9.25" style="1" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="15" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="10" width="7.75" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="9.25" style="1" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="15" style="1" bestFit="1" customWidth="1"/>
-    <col min="13" max="14" width="7.75" style="1" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="37.5" style="1" bestFit="1" customWidth="1"/>
-    <col min="16" max="16384" width="9" style="1"/>
+    <col min="6" max="6" width="6.75" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="5.75" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="9.25" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="15" style="1" bestFit="1" customWidth="1"/>
+    <col min="10" max="11" width="8.625" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="6.125" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="9.25" style="1" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="15" style="1" bestFit="1" customWidth="1"/>
+    <col min="15" max="16" width="7.75" style="1" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="37.5" style="1" bestFit="1" customWidth="1"/>
+    <col min="18" max="16384" width="9" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:15" s="4" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:17" s="4" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A1" s="5" t="s">
         <v>5</v>
       </c>
@@ -920,39 +1082,31 @@
       <c r="D1" s="5" t="s">
         <v>9</v>
       </c>
-      <c r="F1" s="5" t="s">
+      <c r="F1" s="36" t="s">
+        <v>55</v>
+      </c>
+      <c r="G1" s="36" t="s">
         <v>65</v>
       </c>
-      <c r="G1" s="5" t="s">
-        <v>63</v>
-      </c>
-      <c r="H1" s="5" t="s">
-        <v>64</v>
-      </c>
-      <c r="I1" s="9">
-        <v>72000000</v>
-      </c>
-      <c r="J1" s="5" t="s">
-        <v>66</v>
-      </c>
-      <c r="K1" s="5" t="s">
-        <v>63</v>
-      </c>
-      <c r="L1" s="5" t="s">
-        <v>64</v>
-      </c>
-      <c r="M1" s="9">
-        <v>168000000</v>
-      </c>
-      <c r="N1" s="5" t="s">
-        <v>66</v>
-      </c>
-      <c r="O1" s="5" t="s">
-        <v>67</v>
-      </c>
-    </row>
-    <row r="2" spans="1:15" x14ac:dyDescent="0.2">
-      <c r="A2" s="24" t="s">
+      <c r="H1" s="42" t="s">
+        <v>79</v>
+      </c>
+      <c r="I1" s="43"/>
+      <c r="J1" s="43"/>
+      <c r="K1" s="44"/>
+      <c r="L1" s="39" t="s">
+        <v>80</v>
+      </c>
+      <c r="M1" s="40"/>
+      <c r="N1" s="40"/>
+      <c r="O1" s="40"/>
+      <c r="P1" s="41"/>
+      <c r="Q1" s="36" t="s">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="2" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="A2" s="21" t="s">
         <v>0</v>
       </c>
       <c r="B2" s="3">
@@ -961,196 +1115,199 @@
       <c r="C2" s="6" t="s">
         <v>4</v>
       </c>
-      <c r="D2" s="23"/>
-      <c r="F2" s="10" t="s">
+      <c r="D2" s="20"/>
+      <c r="E2" s="18"/>
+      <c r="F2" s="37"/>
+      <c r="G2" s="37"/>
+      <c r="H2" s="23" t="s">
+        <v>53</v>
+      </c>
+      <c r="I2" s="23" t="s">
+        <v>54</v>
+      </c>
+      <c r="J2" s="9" t="s">
+        <v>68</v>
+      </c>
+      <c r="K2" s="5" t="s">
+        <v>56</v>
+      </c>
+      <c r="L2" s="23" t="s">
+        <v>64</v>
+      </c>
+      <c r="M2" s="23" t="s">
+        <v>53</v>
+      </c>
+      <c r="N2" s="5" t="s">
+        <v>54</v>
+      </c>
+      <c r="O2" s="9" t="s">
+        <v>68</v>
+      </c>
+      <c r="P2" s="5" t="s">
+        <v>56</v>
+      </c>
+      <c r="Q2" s="37"/>
+    </row>
+    <row r="3" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="A3" s="21"/>
+      <c r="B3" s="3">
+        <v>1</v>
+      </c>
+      <c r="C3" s="20"/>
+      <c r="D3" s="6" t="s">
+        <v>48</v>
+      </c>
+      <c r="E3" s="18"/>
+      <c r="F3" s="35" t="s">
         <v>49</v>
       </c>
-      <c r="G2" s="11">
-        <v>72</v>
-      </c>
-      <c r="H2" s="11">
+      <c r="G3" s="34" t="s">
+        <v>66</v>
+      </c>
+      <c r="H3" s="22"/>
+      <c r="I3" s="10"/>
+      <c r="J3" s="11" t="e">
+        <f>$J$2/(H3*I3)</f>
+        <v>#VALUE!</v>
+      </c>
+      <c r="K3" s="10" t="e">
+        <f>_xlfn.LET(_xlpm.t,1/J3,
+ IF(_xlpm.t&lt;0.000001, TEXT(_xlpm.t*1000000000,"0.###")&amp;" ns",
+ IF(_xlpm.t&lt;0.001, TEXT(_xlpm.t*1000000,"0.###")&amp;" µs",
+ IF(_xlpm.t&lt;1,    TEXT(_xlpm.t*1000,"0.###")&amp;" ms",
+           TEXT(_xlpm.t,"0.###")&amp;" s"))))</f>
+        <v>#VALUE!</v>
+      </c>
+      <c r="L3" s="25">
+        <v>168</v>
+      </c>
+      <c r="M3" s="10">
+        <v>168</v>
+      </c>
+      <c r="N3" s="11">
         <v>10</v>
       </c>
-      <c r="I2" s="12">
-        <f>$I$1/(G2*H2)</f>
+      <c r="O3" s="31">
+        <f>L3*1000000/(M3*N3)</f>
         <v>100000</v>
       </c>
-      <c r="J2" s="13" t="str">
-        <f>_xlfn.LET(_xlpm.t,1/I2,
+      <c r="P3" s="12" t="str">
+        <f>_xlfn.LET(_xlpm.t,1/O3,
  IF(_xlpm.t&lt;0.000001, TEXT(_xlpm.t*1000000000,"0.###")&amp;" ns",
  IF(_xlpm.t&lt;0.001, TEXT(_xlpm.t*1000000,"0.###")&amp;" µs",
  IF(_xlpm.t&lt;1,    TEXT(_xlpm.t*1000,"0.###")&amp;" ms",
            TEXT(_xlpm.t,"0.###")&amp;" s"))))</f>
         <v>10. µs</v>
       </c>
-      <c r="K2" s="10">
-        <v>168</v>
-      </c>
-      <c r="L2" s="12">
-        <v>10</v>
-      </c>
-      <c r="M2" s="12">
-        <f>$M$1/(K2*L2)</f>
-        <v>100000</v>
-      </c>
-      <c r="N2" s="13" t="str">
-        <f>_xlfn.LET(_xlpm.t,1/M2,
+      <c r="Q3" s="38" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="4" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="A4" s="21"/>
+      <c r="B4" s="3">
+        <v>2</v>
+      </c>
+      <c r="C4" s="20"/>
+      <c r="D4" s="8" t="s">
+        <v>43</v>
+      </c>
+      <c r="E4" s="18"/>
+      <c r="F4" s="28" t="s">
+        <v>50</v>
+      </c>
+      <c r="G4" s="32" t="s">
+        <v>67</v>
+      </c>
+      <c r="H4" s="22"/>
+      <c r="J4" s="13" t="e">
+        <f>$J$2/(H4*I4)</f>
+        <v>#VALUE!</v>
+      </c>
+      <c r="K4" s="22" t="e">
+        <f t="shared" ref="K4:K16" si="0">_xlfn.LET(_xlpm.t,1/J4,
  IF(_xlpm.t&lt;0.000001, TEXT(_xlpm.t*1000000000,"0.###")&amp;" ns",
  IF(_xlpm.t&lt;0.001, TEXT(_xlpm.t*1000000,"0.###")&amp;" µs",
  IF(_xlpm.t&lt;1,    TEXT(_xlpm.t*1000,"0.###")&amp;" ms",
            TEXT(_xlpm.t,"0.###")&amp;" s"))))</f>
-        <v>10. µs</v>
-      </c>
-      <c r="O2" s="21" t="s">
-        <v>68</v>
-      </c>
-    </row>
-    <row r="3" spans="1:15" x14ac:dyDescent="0.2">
-      <c r="A3" s="24"/>
-      <c r="B3" s="3">
-        <v>1</v>
-      </c>
-      <c r="C3" s="23"/>
-      <c r="D3" s="6" t="s">
-        <v>48</v>
-      </c>
-      <c r="F3" s="14" t="s">
+        <v>#VALUE!</v>
+      </c>
+      <c r="L4" s="24">
+        <v>84</v>
+      </c>
+      <c r="M4" s="22">
+        <v>336</v>
+      </c>
+      <c r="N4" s="13">
         <v>50</v>
       </c>
-      <c r="G3" s="1">
-        <v>288</v>
-      </c>
-      <c r="H3" s="1">
-        <v>50</v>
-      </c>
-      <c r="I3" s="15">
-        <f t="shared" ref="I3:I15" si="0">$I$1/(G3*H3)</f>
+      <c r="O4" s="31">
+        <f t="shared" ref="O4:O16" si="1">L4*1000000/(M4*N4)</f>
         <v>5000</v>
       </c>
-      <c r="J3" s="16" t="str">
-        <f t="shared" ref="J3:J15" si="1">_xlfn.LET(_xlpm.t,1/I3,
+      <c r="P4" s="14" t="str">
+        <f t="shared" ref="P4:P16" si="2">_xlfn.LET(_xlpm.t,1/O4,
  IF(_xlpm.t&lt;0.000001, TEXT(_xlpm.t*1000000000,"0.###")&amp;" ns",
  IF(_xlpm.t&lt;0.001, TEXT(_xlpm.t*1000000,"0.###")&amp;" µs",
  IF(_xlpm.t&lt;1,    TEXT(_xlpm.t*1000,"0.###")&amp;" ms",
            TEXT(_xlpm.t,"0.###")&amp;" s"))))</f>
         <v>200. µs</v>
       </c>
-      <c r="K3" s="14">
-        <v>672</v>
-      </c>
-      <c r="L3" s="15">
+      <c r="Q4" s="18" t="s">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="5" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="A5" s="21"/>
+      <c r="B5" s="3">
+        <v>3</v>
+      </c>
+      <c r="C5" s="20"/>
+      <c r="D5" s="8" t="s">
+        <v>44</v>
+      </c>
+      <c r="F5" s="28" t="s">
+        <v>51</v>
+      </c>
+      <c r="G5" s="32" t="s">
+        <v>67</v>
+      </c>
+      <c r="H5" s="22"/>
+      <c r="J5" s="13" t="e">
+        <f>$J$2/(H5*I5)</f>
+        <v>#VALUE!</v>
+      </c>
+      <c r="K5" s="22" t="e">
+        <f t="shared" si="0"/>
+        <v>#VALUE!</v>
+      </c>
+      <c r="L5" s="24">
+        <v>84</v>
+      </c>
+      <c r="M5" s="22">
+        <v>336</v>
+      </c>
+      <c r="N5" s="13">
         <v>50</v>
       </c>
-      <c r="M3" s="15">
-        <f t="shared" ref="M3:M15" si="2">$M$1/(K3*L3)</f>
+      <c r="O5" s="31">
+        <f t="shared" si="1"/>
         <v>5000</v>
       </c>
-      <c r="N3" s="16" t="str">
-        <f t="shared" ref="N3:N15" si="3">_xlfn.LET(_xlpm.t,1/M3,
+      <c r="P5" s="14" t="str">
+        <f t="shared" ref="P5" si="3">_xlfn.LET(_xlpm.t,1/O5,
  IF(_xlpm.t&lt;0.000001, TEXT(_xlpm.t*1000000000,"0.###")&amp;" ns",
  IF(_xlpm.t&lt;0.001, TEXT(_xlpm.t*1000000,"0.###")&amp;" µs",
  IF(_xlpm.t&lt;1,    TEXT(_xlpm.t*1000,"0.###")&amp;" ms",
            TEXT(_xlpm.t,"0.###")&amp;" s"))))</f>
         <v>200. µs</v>
       </c>
-      <c r="O3" s="21" t="s">
-        <v>72</v>
-      </c>
-    </row>
-    <row r="4" spans="1:15" x14ac:dyDescent="0.2">
-      <c r="A4" s="24"/>
-      <c r="B4" s="3">
-        <v>2</v>
-      </c>
-      <c r="C4" s="23"/>
-      <c r="D4" s="8" t="s">
-        <v>43</v>
-      </c>
-      <c r="F4" s="14" t="s">
-        <v>51</v>
-      </c>
-      <c r="G4" s="1">
-        <v>7200</v>
-      </c>
-      <c r="H4" s="1">
-        <v>1000</v>
-      </c>
-      <c r="I4" s="15">
-        <f t="shared" si="0"/>
-        <v>10</v>
-      </c>
-      <c r="J4" s="16" t="str">
-        <f t="shared" si="1"/>
-        <v>100. ms</v>
-      </c>
-      <c r="K4" s="14">
-        <v>672</v>
-      </c>
-      <c r="L4" s="15">
-        <v>50</v>
-      </c>
-      <c r="M4" s="15">
-        <f t="shared" ref="M4" si="4">$M$1/(K4*L4)</f>
-        <v>5000</v>
-      </c>
-      <c r="N4" s="16" t="str">
-        <f t="shared" ref="N4" si="5">_xlfn.LET(_xlpm.t,1/M4,
- IF(_xlpm.t&lt;0.000001, TEXT(_xlpm.t*1000000000,"0.###")&amp;" ns",
- IF(_xlpm.t&lt;0.001, TEXT(_xlpm.t*1000000,"0.###")&amp;" µs",
- IF(_xlpm.t&lt;1,    TEXT(_xlpm.t*1000,"0.###")&amp;" ms",
-           TEXT(_xlpm.t,"0.###")&amp;" s"))))</f>
-        <v>200. µs</v>
-      </c>
-      <c r="O4" s="21" t="s">
-        <v>73</v>
-      </c>
-    </row>
-    <row r="5" spans="1:15" x14ac:dyDescent="0.2">
-      <c r="A5" s="24"/>
-      <c r="B5" s="3">
-        <v>3</v>
-      </c>
-      <c r="C5" s="23"/>
-      <c r="D5" s="8" t="s">
-        <v>44</v>
-      </c>
-      <c r="F5" s="14" t="s">
-        <v>52</v>
-      </c>
-      <c r="G5" s="1">
-        <v>7200</v>
-      </c>
-      <c r="H5" s="1">
-        <v>10</v>
-      </c>
-      <c r="I5" s="15">
-        <f t="shared" si="0"/>
-        <v>1000</v>
-      </c>
-      <c r="J5" s="16" t="str">
-        <f t="shared" si="1"/>
-        <v>1. ms</v>
-      </c>
-      <c r="K5" s="14">
-        <v>16800</v>
-      </c>
-      <c r="L5" s="15">
-        <v>10</v>
-      </c>
-      <c r="M5" s="15">
-        <f t="shared" si="2"/>
-        <v>1000</v>
-      </c>
-      <c r="N5" s="16" t="str">
-        <f t="shared" si="3"/>
-        <v>1. ms</v>
-      </c>
-      <c r="O5" s="21" t="s">
-        <v>69</v>
-      </c>
-    </row>
-    <row r="6" spans="1:15" x14ac:dyDescent="0.2">
-      <c r="A6" s="24"/>
+      <c r="Q5" s="18" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="6" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="A6" s="21"/>
       <c r="B6" s="3">
         <v>4</v>
       </c>
@@ -1160,336 +1317,442 @@
       <c r="D6" s="2" t="s">
         <v>45</v>
       </c>
-      <c r="E6" s="1" t="s">
-        <v>71</v>
-      </c>
-      <c r="F6" s="14" t="s">
-        <v>53</v>
-      </c>
-      <c r="I6" s="15" t="e">
+      <c r="F6" s="28" t="s">
+        <v>52</v>
+      </c>
+      <c r="G6" s="32" t="s">
+        <v>67</v>
+      </c>
+      <c r="H6" s="22"/>
+      <c r="J6" s="13" t="e">
+        <f>$J$2/(H6*I6)</f>
+        <v>#VALUE!</v>
+      </c>
+      <c r="K6" s="22" t="e">
         <f t="shared" si="0"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="J6" s="16" t="e">
+        <v>#VALUE!</v>
+      </c>
+      <c r="L6" s="24">
+        <v>84</v>
+      </c>
+      <c r="M6" s="22">
+        <v>8400</v>
+      </c>
+      <c r="N6" s="13">
+        <v>10</v>
+      </c>
+      <c r="O6" s="31">
+        <f t="shared" si="1"/>
+        <v>1000</v>
+      </c>
+      <c r="P6" s="14" t="str">
+        <f t="shared" si="2"/>
+        <v>1. ms</v>
+      </c>
+      <c r="Q6" s="18" t="s">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="7" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="A7" s="21"/>
+      <c r="B7" s="3">
+        <v>5</v>
+      </c>
+      <c r="C7" s="7" t="s">
+        <v>23</v>
+      </c>
+      <c r="D7" s="2" t="s">
+        <v>47</v>
+      </c>
+      <c r="F7" s="28" t="s">
+        <v>73</v>
+      </c>
+      <c r="G7" s="32" t="s">
+        <v>67</v>
+      </c>
+      <c r="H7" s="22"/>
+      <c r="J7" s="13" t="e">
+        <f>$J$2/(H7*I7)</f>
+        <v>#VALUE!</v>
+      </c>
+      <c r="K7" s="22" t="e">
+        <f t="shared" si="0"/>
+        <v>#VALUE!</v>
+      </c>
+      <c r="L7" s="24">
+        <v>84</v>
+      </c>
+      <c r="M7" s="22">
+        <v>84</v>
+      </c>
+      <c r="N7" s="13">
+        <v>25</v>
+      </c>
+      <c r="O7" s="31">
+        <f t="shared" si="1"/>
+        <v>40000</v>
+      </c>
+      <c r="P7" s="14" t="str">
+        <f t="shared" si="2"/>
+        <v>25. µs</v>
+      </c>
+      <c r="Q7" s="18" t="s">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="8" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="A8" s="21"/>
+      <c r="B8" s="3">
+        <v>6</v>
+      </c>
+      <c r="C8" s="7" t="s">
+        <v>24</v>
+      </c>
+      <c r="D8" s="2" t="s">
+        <v>63</v>
+      </c>
+      <c r="F8" s="28" t="s">
+        <v>74</v>
+      </c>
+      <c r="G8" s="32" t="s">
+        <v>67</v>
+      </c>
+      <c r="H8" s="22"/>
+      <c r="J8" s="13" t="e">
+        <f>$J$2/(H8*I8)</f>
+        <v>#VALUE!</v>
+      </c>
+      <c r="K8" s="22" t="e">
+        <f t="shared" si="0"/>
+        <v>#VALUE!</v>
+      </c>
+      <c r="L8" s="24">
+        <v>84</v>
+      </c>
+      <c r="M8" s="22"/>
+      <c r="N8" s="13"/>
+      <c r="O8" s="31" t="e">
         <f t="shared" si="1"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="K6" s="14"/>
-      <c r="L6" s="15"/>
-      <c r="M6" s="15" t="e">
+      <c r="P8" s="14" t="e">
         <f t="shared" si="2"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="N6" s="16" t="e">
-        <f t="shared" si="3"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="O6" s="21"/>
-    </row>
-    <row r="7" spans="1:15" x14ac:dyDescent="0.2">
-      <c r="A7" s="24"/>
-      <c r="B7" s="3">
-        <v>5</v>
-      </c>
-      <c r="C7" s="7" t="s">
-        <v>23</v>
-      </c>
-      <c r="D7" s="2" t="s">
-        <v>47</v>
-      </c>
-      <c r="E7" s="1" t="s">
-        <v>70</v>
-      </c>
-      <c r="F7" s="14" t="s">
-        <v>54</v>
-      </c>
-      <c r="I7" s="15" t="e">
+      <c r="Q8" s="18"/>
+    </row>
+    <row r="9" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="A9" s="21"/>
+      <c r="B9" s="3">
+        <v>7</v>
+      </c>
+      <c r="C9" s="7" t="s">
+        <v>25</v>
+      </c>
+      <c r="D9" s="2"/>
+      <c r="F9" s="28" t="s">
+        <v>75</v>
+      </c>
+      <c r="G9" s="32" t="s">
+        <v>67</v>
+      </c>
+      <c r="H9" s="22"/>
+      <c r="J9" s="13" t="e">
+        <f>$J$2/(H9*I9)</f>
+        <v>#VALUE!</v>
+      </c>
+      <c r="K9" s="22" t="e">
         <f t="shared" si="0"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="J7" s="16" t="e">
+        <v>#VALUE!</v>
+      </c>
+      <c r="L9" s="24">
+        <v>84</v>
+      </c>
+      <c r="M9" s="22"/>
+      <c r="N9" s="13"/>
+      <c r="O9" s="31" t="e">
         <f t="shared" si="1"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="K7" s="14"/>
-      <c r="L7" s="15"/>
-      <c r="M7" s="15" t="e">
+      <c r="P9" s="14" t="e">
         <f t="shared" si="2"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="N7" s="16" t="e">
-        <f t="shared" si="3"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="O7" s="21"/>
-    </row>
-    <row r="8" spans="1:15" x14ac:dyDescent="0.2">
-      <c r="A8" s="24"/>
-      <c r="B8" s="3">
-        <v>6</v>
-      </c>
-      <c r="C8" s="7" t="s">
-        <v>24</v>
-      </c>
-      <c r="D8" s="2"/>
-      <c r="F8" s="14" t="s">
-        <v>55</v>
-      </c>
-      <c r="I8" s="15" t="e">
+      <c r="Q9" s="18"/>
+    </row>
+    <row r="10" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="A10" s="21"/>
+      <c r="B10" s="3">
+        <v>8</v>
+      </c>
+      <c r="C10" s="2"/>
+      <c r="D10" s="2"/>
+      <c r="F10" s="29" t="s">
+        <v>69</v>
+      </c>
+      <c r="G10" s="27" t="s">
+        <v>66</v>
+      </c>
+      <c r="H10" s="22"/>
+      <c r="J10" s="13" t="e">
+        <f>$J$2/(H10*I10)</f>
+        <v>#VALUE!</v>
+      </c>
+      <c r="K10" s="22" t="e">
         <f t="shared" si="0"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="J8" s="16" t="e">
+        <v>#VALUE!</v>
+      </c>
+      <c r="L10" s="24">
+        <v>168</v>
+      </c>
+      <c r="M10" s="22"/>
+      <c r="N10" s="13"/>
+      <c r="O10" s="31" t="e">
         <f t="shared" si="1"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="K8" s="14"/>
-      <c r="L8" s="15"/>
-      <c r="M8" s="15" t="e">
+      <c r="P10" s="14" t="e">
         <f t="shared" si="2"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="N8" s="16" t="e">
-        <f t="shared" si="3"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="O8" s="21"/>
-    </row>
-    <row r="9" spans="1:15" x14ac:dyDescent="0.2">
-      <c r="A9" s="24"/>
-      <c r="B9" s="3">
-        <v>7</v>
-      </c>
-      <c r="C9" s="7" t="s">
-        <v>25</v>
-      </c>
-      <c r="D9" s="2"/>
-      <c r="F9" s="14" t="s">
-        <v>56</v>
-      </c>
-      <c r="I9" s="15" t="e">
+      <c r="Q10" s="18"/>
+    </row>
+    <row r="11" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="A11" s="21"/>
+      <c r="B11" s="2">
+        <v>9</v>
+      </c>
+      <c r="C11" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="D11" s="2"/>
+      <c r="F11" s="29" t="s">
+        <v>70</v>
+      </c>
+      <c r="G11" s="27" t="s">
+        <v>66</v>
+      </c>
+      <c r="H11" s="22"/>
+      <c r="J11" s="13" t="e">
+        <f>$J$2/(H11*I11)</f>
+        <v>#VALUE!</v>
+      </c>
+      <c r="K11" s="22" t="e">
         <f t="shared" si="0"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="J9" s="16" t="e">
+        <v>#VALUE!</v>
+      </c>
+      <c r="L11" s="24">
+        <v>168</v>
+      </c>
+      <c r="M11" s="22"/>
+      <c r="O11" s="31" t="e">
         <f t="shared" si="1"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="K9" s="14"/>
-      <c r="L9" s="15"/>
-      <c r="M9" s="15" t="e">
+      <c r="P11" s="14" t="e">
         <f t="shared" si="2"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="N9" s="16" t="e">
-        <f t="shared" si="3"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="O9" s="21"/>
-    </row>
-    <row r="10" spans="1:15" x14ac:dyDescent="0.2">
-      <c r="A10" s="24"/>
-      <c r="B10" s="3">
-        <v>8</v>
-      </c>
-      <c r="C10" s="2"/>
-      <c r="D10" s="2"/>
-      <c r="F10" s="14" t="s">
-        <v>57</v>
-      </c>
-      <c r="I10" s="15" t="e">
+      <c r="Q11" s="18"/>
+    </row>
+    <row r="12" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="A12" s="21"/>
+      <c r="B12" s="2">
+        <v>10</v>
+      </c>
+      <c r="C12" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="D12" s="2"/>
+      <c r="F12" s="29" t="s">
+        <v>71</v>
+      </c>
+      <c r="G12" s="27" t="s">
+        <v>66</v>
+      </c>
+      <c r="H12" s="22"/>
+      <c r="J12" s="13" t="e">
+        <f>$J$2/(H12*I12)</f>
+        <v>#VALUE!</v>
+      </c>
+      <c r="K12" s="22" t="e">
         <f t="shared" si="0"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="J10" s="16" t="e">
+        <v>#VALUE!</v>
+      </c>
+      <c r="L12" s="24">
+        <v>168</v>
+      </c>
+      <c r="M12" s="22"/>
+      <c r="N12" s="13"/>
+      <c r="O12" s="31" t="e">
         <f t="shared" si="1"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="K10" s="14"/>
-      <c r="M10" s="15" t="e">
+      <c r="P12" s="14" t="e">
         <f t="shared" si="2"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="N10" s="16" t="e">
-        <f t="shared" si="3"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="O10" s="21"/>
-    </row>
-    <row r="11" spans="1:15" x14ac:dyDescent="0.2">
-      <c r="A11" s="24"/>
-      <c r="B11" s="2">
-        <v>9</v>
-      </c>
-      <c r="C11" s="2" t="s">
-        <v>15</v>
-      </c>
-      <c r="D11" s="2"/>
-      <c r="F11" s="14" t="s">
-        <v>58</v>
-      </c>
-      <c r="I11" s="15" t="e">
+      <c r="Q12" s="18"/>
+    </row>
+    <row r="13" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="A13" s="21"/>
+      <c r="B13" s="2">
+        <v>11</v>
+      </c>
+      <c r="C13" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="D13" s="2"/>
+      <c r="F13" s="29" t="s">
+        <v>72</v>
+      </c>
+      <c r="G13" s="27" t="s">
+        <v>66</v>
+      </c>
+      <c r="H13" s="22"/>
+      <c r="J13" s="13" t="e">
+        <f>$J$2/(H13*I13)</f>
+        <v>#VALUE!</v>
+      </c>
+      <c r="K13" s="22" t="e">
         <f t="shared" si="0"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="J11" s="16" t="e">
+        <v>#VALUE!</v>
+      </c>
+      <c r="L13" s="24">
+        <v>168</v>
+      </c>
+      <c r="M13" s="22"/>
+      <c r="N13" s="13"/>
+      <c r="O13" s="31" t="e">
         <f t="shared" si="1"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="K11" s="14"/>
-      <c r="L11" s="15"/>
-      <c r="M11" s="15" t="e">
+      <c r="P13" s="14" t="e">
         <f t="shared" si="2"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="N11" s="16" t="e">
-        <f t="shared" si="3"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="O11" s="21"/>
-    </row>
-    <row r="12" spans="1:15" x14ac:dyDescent="0.2">
-      <c r="A12" s="24"/>
-      <c r="B12" s="2">
-        <v>10</v>
-      </c>
-      <c r="C12" s="2" t="s">
-        <v>16</v>
-      </c>
-      <c r="D12" s="2"/>
-      <c r="F12" s="14" t="s">
-        <v>59</v>
-      </c>
-      <c r="I12" s="15" t="e">
+      <c r="Q13" s="18"/>
+    </row>
+    <row r="14" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="A14" s="21"/>
+      <c r="B14" s="2">
+        <v>12</v>
+      </c>
+      <c r="C14" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="D14" s="2"/>
+      <c r="F14" s="28" t="s">
+        <v>76</v>
+      </c>
+      <c r="G14" s="32" t="s">
+        <v>67</v>
+      </c>
+      <c r="H14" s="22"/>
+      <c r="J14" s="13" t="e">
+        <f>$J$2/(H14*I14)</f>
+        <v>#VALUE!</v>
+      </c>
+      <c r="K14" s="22" t="e">
         <f t="shared" si="0"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="J12" s="16" t="e">
+        <v>#VALUE!</v>
+      </c>
+      <c r="L14" s="24">
+        <v>84</v>
+      </c>
+      <c r="M14" s="22"/>
+      <c r="N14" s="13"/>
+      <c r="O14" s="31" t="e">
         <f t="shared" si="1"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="K12" s="14"/>
-      <c r="L12" s="15"/>
-      <c r="M12" s="15" t="e">
+      <c r="P14" s="14" t="e">
         <f t="shared" si="2"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="N12" s="16" t="e">
-        <f t="shared" si="3"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="O12" s="21"/>
-    </row>
-    <row r="13" spans="1:15" x14ac:dyDescent="0.2">
-      <c r="A13" s="24"/>
-      <c r="B13" s="2">
-        <v>11</v>
-      </c>
-      <c r="C13" s="2" t="s">
-        <v>17</v>
-      </c>
-      <c r="D13" s="2"/>
-      <c r="F13" s="14" t="s">
-        <v>60</v>
-      </c>
-      <c r="I13" s="15" t="e">
+      <c r="Q14" s="18"/>
+    </row>
+    <row r="15" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="A15" s="21"/>
+      <c r="B15" s="2">
+        <v>13</v>
+      </c>
+      <c r="C15" s="6" t="s">
+        <v>19</v>
+      </c>
+      <c r="D15" s="20"/>
+      <c r="F15" s="28" t="s">
+        <v>77</v>
+      </c>
+      <c r="G15" s="32" t="s">
+        <v>67</v>
+      </c>
+      <c r="H15" s="22"/>
+      <c r="J15" s="13" t="e">
+        <f>$J$2/(H15*I15)</f>
+        <v>#VALUE!</v>
+      </c>
+      <c r="K15" s="22" t="e">
         <f t="shared" si="0"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="J13" s="16" t="e">
+        <v>#VALUE!</v>
+      </c>
+      <c r="L15" s="24">
+        <v>84</v>
+      </c>
+      <c r="M15" s="22"/>
+      <c r="N15" s="13"/>
+      <c r="O15" s="31" t="e">
         <f t="shared" si="1"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="K13" s="14"/>
-      <c r="L13" s="15"/>
-      <c r="M13" s="15" t="e">
+      <c r="P15" s="14" t="e">
         <f t="shared" si="2"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="N13" s="16" t="e">
-        <f t="shared" si="3"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="O13" s="21"/>
-    </row>
-    <row r="14" spans="1:15" x14ac:dyDescent="0.2">
-      <c r="A14" s="24"/>
-      <c r="B14" s="2">
-        <v>12</v>
-      </c>
-      <c r="C14" s="2" t="s">
-        <v>18</v>
-      </c>
-      <c r="D14" s="2"/>
-      <c r="F14" s="14" t="s">
-        <v>61</v>
-      </c>
-      <c r="I14" s="15" t="e">
+      <c r="Q15" s="18"/>
+    </row>
+    <row r="16" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="A16" s="21"/>
+      <c r="B16" s="2">
+        <v>14</v>
+      </c>
+      <c r="C16" s="8" t="s">
+        <v>20</v>
+      </c>
+      <c r="D16" s="20"/>
+      <c r="F16" s="30" t="s">
+        <v>78</v>
+      </c>
+      <c r="G16" s="33" t="s">
+        <v>67</v>
+      </c>
+      <c r="H16" s="16"/>
+      <c r="I16" s="15"/>
+      <c r="J16" s="16" t="e">
+        <f>$J$2/(H16*I16)</f>
+        <v>#VALUE!</v>
+      </c>
+      <c r="K16" s="15" t="e">
         <f t="shared" si="0"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="J14" s="16" t="e">
+        <v>#VALUE!</v>
+      </c>
+      <c r="L16" s="26">
+        <v>84</v>
+      </c>
+      <c r="M16" s="15"/>
+      <c r="N16" s="16"/>
+      <c r="O16" s="16" t="e">
         <f t="shared" si="1"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="K14" s="14"/>
-      <c r="L14" s="15"/>
-      <c r="M14" s="15" t="e">
+      <c r="P16" s="17" t="e">
         <f t="shared" si="2"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="N14" s="16" t="e">
-        <f t="shared" si="3"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="O14" s="21"/>
-    </row>
-    <row r="15" spans="1:15" x14ac:dyDescent="0.2">
-      <c r="A15" s="24"/>
-      <c r="B15" s="2">
-        <v>13</v>
-      </c>
-      <c r="C15" s="6" t="s">
-        <v>19</v>
-      </c>
-      <c r="D15" s="23"/>
-      <c r="F15" s="17" t="s">
-        <v>62</v>
-      </c>
-      <c r="G15" s="18"/>
-      <c r="H15" s="18"/>
-      <c r="I15" s="19" t="e">
-        <f t="shared" si="0"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="J15" s="20" t="e">
-        <f t="shared" si="1"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="K15" s="17"/>
-      <c r="L15" s="19"/>
-      <c r="M15" s="19" t="e">
-        <f t="shared" si="2"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="N15" s="20" t="e">
-        <f t="shared" si="3"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="O15" s="22"/>
-    </row>
-    <row r="16" spans="1:15" x14ac:dyDescent="0.2">
-      <c r="A16" s="24"/>
-      <c r="B16" s="2">
-        <v>14</v>
-      </c>
-      <c r="C16" s="8" t="s">
-        <v>20</v>
-      </c>
-      <c r="D16" s="23"/>
+      <c r="Q16" s="19"/>
     </row>
     <row r="17" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A17" s="24"/>
+      <c r="A17" s="21"/>
       <c r="B17" s="3">
         <v>15</v>
       </c>
@@ -1497,7 +1760,7 @@
       <c r="D17" s="2"/>
     </row>
     <row r="18" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A18" s="24" t="s">
+      <c r="A18" s="21" t="s">
         <v>1</v>
       </c>
       <c r="B18" s="3">
@@ -1507,7 +1770,7 @@
       <c r="D18" s="2"/>
     </row>
     <row r="19" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A19" s="24"/>
+      <c r="A19" s="21"/>
       <c r="B19" s="3">
         <v>1</v>
       </c>
@@ -1515,17 +1778,17 @@
       <c r="D19" s="2"/>
     </row>
     <row r="20" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A20" s="24"/>
+      <c r="A20" s="21"/>
       <c r="B20" s="2">
         <v>2</v>
       </c>
       <c r="C20" s="6" t="s">
         <v>46</v>
       </c>
-      <c r="D20" s="23"/>
+      <c r="D20" s="20"/>
     </row>
     <row r="21" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A21" s="24"/>
+      <c r="A21" s="21"/>
       <c r="B21" s="2">
         <v>3</v>
       </c>
@@ -1535,7 +1798,7 @@
       <c r="D21" s="2"/>
     </row>
     <row r="22" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A22" s="24"/>
+      <c r="A22" s="21"/>
       <c r="B22" s="3">
         <v>4</v>
       </c>
@@ -1543,7 +1806,7 @@
       <c r="D22" s="2"/>
     </row>
     <row r="23" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A23" s="24"/>
+      <c r="A23" s="21"/>
       <c r="B23" s="3">
         <v>5</v>
       </c>
@@ -1551,103 +1814,103 @@
       <c r="D23" s="2"/>
     </row>
     <row r="24" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A24" s="24"/>
+      <c r="A24" s="21"/>
       <c r="B24" s="3">
         <v>6</v>
       </c>
-      <c r="C24" s="23"/>
+      <c r="C24" s="20"/>
       <c r="D24" s="6" t="s">
         <v>36</v>
       </c>
     </row>
     <row r="25" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A25" s="24"/>
+      <c r="A25" s="21"/>
       <c r="B25" s="3">
         <v>7</v>
       </c>
-      <c r="C25" s="23"/>
+      <c r="C25" s="20"/>
       <c r="D25" s="8" t="s">
         <v>37</v>
       </c>
     </row>
     <row r="26" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A26" s="24"/>
+      <c r="A26" s="21"/>
       <c r="B26" s="3">
         <v>8</v>
       </c>
-      <c r="C26" s="23"/>
+      <c r="C26" s="20"/>
       <c r="D26" s="8"/>
     </row>
     <row r="27" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A27" s="24"/>
+      <c r="A27" s="21"/>
       <c r="B27" s="3">
         <v>9</v>
       </c>
-      <c r="C27" s="23"/>
+      <c r="C27" s="20"/>
       <c r="D27" s="8"/>
     </row>
     <row r="28" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A28" s="24"/>
+      <c r="A28" s="21"/>
       <c r="B28" s="3">
         <v>10</v>
       </c>
-      <c r="C28" s="23"/>
+      <c r="C28" s="20"/>
       <c r="D28" s="8" t="s">
         <v>41</v>
       </c>
     </row>
     <row r="29" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A29" s="24"/>
+      <c r="A29" s="21"/>
       <c r="B29" s="3">
         <v>11</v>
       </c>
-      <c r="C29" s="23"/>
+      <c r="C29" s="20"/>
       <c r="D29" s="8" t="s">
         <v>42</v>
       </c>
     </row>
     <row r="30" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A30" s="24"/>
+      <c r="A30" s="21"/>
       <c r="B30" s="3">
         <v>12</v>
       </c>
-      <c r="C30" s="23"/>
+      <c r="C30" s="20"/>
       <c r="D30" s="8" t="s">
         <v>35</v>
       </c>
     </row>
     <row r="31" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A31" s="24"/>
+      <c r="A31" s="21"/>
       <c r="B31" s="3">
         <v>13</v>
       </c>
-      <c r="C31" s="23"/>
+      <c r="C31" s="20"/>
       <c r="D31" s="8" t="s">
         <v>38</v>
       </c>
     </row>
     <row r="32" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A32" s="24"/>
+      <c r="A32" s="21"/>
       <c r="B32" s="3">
         <v>14</v>
       </c>
-      <c r="C32" s="23"/>
+      <c r="C32" s="20"/>
       <c r="D32" s="8" t="s">
         <v>39</v>
       </c>
     </row>
     <row r="33" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A33" s="24"/>
+      <c r="A33" s="21"/>
       <c r="B33" s="3">
         <v>15</v>
       </c>
-      <c r="C33" s="23"/>
+      <c r="C33" s="20"/>
       <c r="D33" s="8" t="s">
         <v>40</v>
       </c>
     </row>
     <row r="34" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A34" s="24" t="s">
+      <c r="A34" s="21" t="s">
         <v>2</v>
       </c>
       <c r="B34" s="3">
@@ -1657,7 +1920,7 @@
       <c r="D34" s="2"/>
     </row>
     <row r="35" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A35" s="24"/>
+      <c r="A35" s="21"/>
       <c r="B35" s="3">
         <v>1</v>
       </c>
@@ -1665,7 +1928,7 @@
       <c r="D35" s="2"/>
     </row>
     <row r="36" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A36" s="24"/>
+      <c r="A36" s="21"/>
       <c r="B36" s="3">
         <v>2</v>
       </c>
@@ -1673,7 +1936,7 @@
       <c r="D36" s="2"/>
     </row>
     <row r="37" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A37" s="24"/>
+      <c r="A37" s="21"/>
       <c r="B37" s="3">
         <v>3</v>
       </c>
@@ -1681,7 +1944,7 @@
       <c r="D37" s="2"/>
     </row>
     <row r="38" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A38" s="24"/>
+      <c r="A38" s="21"/>
       <c r="B38" s="3">
         <v>4</v>
       </c>
@@ -1689,7 +1952,7 @@
       <c r="D38" s="2"/>
     </row>
     <row r="39" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A39" s="24"/>
+      <c r="A39" s="21"/>
       <c r="B39" s="3">
         <v>5</v>
       </c>
@@ -1697,7 +1960,7 @@
       <c r="D39" s="2"/>
     </row>
     <row r="40" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A40" s="24"/>
+      <c r="A40" s="21"/>
       <c r="B40" s="3">
         <v>6</v>
       </c>
@@ -1705,7 +1968,7 @@
       <c r="D40" s="2"/>
     </row>
     <row r="41" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A41" s="24"/>
+      <c r="A41" s="21"/>
       <c r="B41" s="3">
         <v>7</v>
       </c>
@@ -1713,7 +1976,7 @@
       <c r="D41" s="2"/>
     </row>
     <row r="42" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A42" s="24"/>
+      <c r="A42" s="21"/>
       <c r="B42" s="3">
         <v>8</v>
       </c>
@@ -1723,7 +1986,7 @@
       <c r="D42" s="2"/>
     </row>
     <row r="43" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A43" s="24"/>
+      <c r="A43" s="21"/>
       <c r="B43" s="3">
         <v>9</v>
       </c>
@@ -1733,7 +1996,7 @@
       <c r="D43" s="2"/>
     </row>
     <row r="44" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A44" s="24"/>
+      <c r="A44" s="21"/>
       <c r="B44" s="3">
         <v>10</v>
       </c>
@@ -1743,7 +2006,7 @@
       <c r="D44" s="2"/>
     </row>
     <row r="45" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A45" s="24"/>
+      <c r="A45" s="21"/>
       <c r="B45" s="3">
         <v>11</v>
       </c>
@@ -1753,7 +2016,7 @@
       <c r="D45" s="2"/>
     </row>
     <row r="46" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A46" s="24"/>
+      <c r="A46" s="21"/>
       <c r="B46" s="3">
         <v>12</v>
       </c>
@@ -1763,7 +2026,7 @@
       <c r="D46" s="2"/>
     </row>
     <row r="47" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A47" s="24"/>
+      <c r="A47" s="21"/>
       <c r="B47" s="3">
         <v>13</v>
       </c>
@@ -1771,7 +2034,7 @@
       <c r="D47" s="2"/>
     </row>
     <row r="48" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A48" s="24"/>
+      <c r="A48" s="21"/>
       <c r="B48" s="2">
         <v>14</v>
       </c>
@@ -1781,7 +2044,7 @@
       <c r="D48" s="8"/>
     </row>
     <row r="49" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A49" s="24"/>
+      <c r="A49" s="21"/>
       <c r="B49" s="2">
         <v>15</v>
       </c>
@@ -1791,7 +2054,7 @@
       <c r="D49" s="8"/>
     </row>
     <row r="50" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A50" s="24" t="s">
+      <c r="A50" s="21" t="s">
         <v>3</v>
       </c>
       <c r="B50" s="3">
@@ -1803,7 +2066,7 @@
       </c>
     </row>
     <row r="51" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A51" s="24"/>
+      <c r="A51" s="21"/>
       <c r="B51" s="3">
         <v>1</v>
       </c>
@@ -1813,7 +2076,7 @@
       </c>
     </row>
     <row r="52" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A52" s="24"/>
+      <c r="A52" s="21"/>
       <c r="B52" s="3">
         <v>2</v>
       </c>
@@ -1823,7 +2086,7 @@
       <c r="D52" s="2"/>
     </row>
     <row r="53" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A53" s="24"/>
+      <c r="A53" s="21"/>
       <c r="B53" s="3">
         <v>3</v>
       </c>
@@ -1833,7 +2096,7 @@
       <c r="D53" s="2"/>
     </row>
     <row r="54" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A54" s="24"/>
+      <c r="A54" s="21"/>
       <c r="B54" s="3">
         <v>4</v>
       </c>
@@ -1841,7 +2104,7 @@
       <c r="D54" s="2"/>
     </row>
     <row r="55" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A55" s="24"/>
+      <c r="A55" s="21"/>
       <c r="B55" s="3">
         <v>5</v>
       </c>
@@ -1849,7 +2112,7 @@
       <c r="D55" s="2"/>
     </row>
     <row r="56" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A56" s="24"/>
+      <c r="A56" s="21"/>
       <c r="B56" s="3">
         <v>6</v>
       </c>
@@ -1857,7 +2120,7 @@
       <c r="D56" s="2"/>
     </row>
     <row r="57" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A57" s="24"/>
+      <c r="A57" s="21"/>
       <c r="B57" s="3">
         <v>7</v>
       </c>
@@ -1865,7 +2128,7 @@
       <c r="D57" s="2"/>
     </row>
     <row r="58" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A58" s="24"/>
+      <c r="A58" s="21"/>
       <c r="B58" s="3">
         <v>8</v>
       </c>
@@ -1873,7 +2136,7 @@
       <c r="D58" s="2"/>
     </row>
     <row r="59" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A59" s="24"/>
+      <c r="A59" s="21"/>
       <c r="B59" s="3">
         <v>9</v>
       </c>
@@ -1881,7 +2144,7 @@
       <c r="D59" s="2"/>
     </row>
     <row r="60" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A60" s="24"/>
+      <c r="A60" s="21"/>
       <c r="B60" s="3">
         <v>10</v>
       </c>
@@ -1889,7 +2152,7 @@
       <c r="D60" s="2"/>
     </row>
     <row r="61" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A61" s="24"/>
+      <c r="A61" s="21"/>
       <c r="B61" s="3">
         <v>11</v>
       </c>
@@ -1897,7 +2160,7 @@
       <c r="D61" s="2"/>
     </row>
     <row r="62" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A62" s="24"/>
+      <c r="A62" s="21"/>
       <c r="B62" s="3">
         <v>12</v>
       </c>
@@ -1905,7 +2168,7 @@
       <c r="D62" s="2"/>
     </row>
     <row r="63" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A63" s="24"/>
+      <c r="A63" s="21"/>
       <c r="B63" s="3">
         <v>13</v>
       </c>
@@ -1913,7 +2176,7 @@
       <c r="D63" s="2"/>
     </row>
     <row r="64" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A64" s="24"/>
+      <c r="A64" s="21"/>
       <c r="B64" s="3">
         <v>14</v>
       </c>
@@ -1921,7 +2184,7 @@
       <c r="D64" s="2"/>
     </row>
     <row r="65" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A65" s="24"/>
+      <c r="A65" s="21"/>
       <c r="B65" s="3">
         <v>15</v>
       </c>
@@ -1929,7 +2192,7 @@
       <c r="D65" s="2"/>
     </row>
     <row r="66" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A66" s="24" t="s">
+      <c r="A66" s="21" t="s">
         <v>8</v>
       </c>
       <c r="B66" s="3">
@@ -1939,7 +2202,7 @@
       <c r="D66" s="2"/>
     </row>
     <row r="67" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A67" s="24"/>
+      <c r="A67" s="21"/>
       <c r="B67" s="3">
         <v>1</v>
       </c>
@@ -1947,7 +2210,7 @@
       <c r="D67" s="2"/>
     </row>
     <row r="68" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A68" s="24"/>
+      <c r="A68" s="21"/>
       <c r="B68" s="3">
         <v>2</v>
       </c>
@@ -1955,7 +2218,7 @@
       <c r="D68" s="2"/>
     </row>
     <row r="69" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A69" s="24"/>
+      <c r="A69" s="21"/>
       <c r="B69" s="3">
         <v>3</v>
       </c>
@@ -1963,7 +2226,7 @@
       <c r="D69" s="2"/>
     </row>
     <row r="70" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A70" s="24"/>
+      <c r="A70" s="21"/>
       <c r="B70" s="3">
         <v>4</v>
       </c>
@@ -1971,7 +2234,7 @@
       <c r="D70" s="2"/>
     </row>
     <row r="71" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A71" s="24"/>
+      <c r="A71" s="21"/>
       <c r="B71" s="3">
         <v>5</v>
       </c>
@@ -1979,7 +2242,7 @@
       <c r="D71" s="2"/>
     </row>
     <row r="72" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A72" s="24"/>
+      <c r="A72" s="21"/>
       <c r="B72" s="3">
         <v>6</v>
       </c>
@@ -1987,7 +2250,7 @@
       <c r="D72" s="2"/>
     </row>
     <row r="73" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A73" s="24"/>
+      <c r="A73" s="21"/>
       <c r="B73" s="3">
         <v>7</v>
       </c>
@@ -1995,7 +2258,7 @@
       <c r="D73" s="2"/>
     </row>
     <row r="74" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A74" s="24"/>
+      <c r="A74" s="21"/>
       <c r="B74" s="3">
         <v>8</v>
       </c>
@@ -2003,7 +2266,7 @@
       <c r="D74" s="2"/>
     </row>
     <row r="75" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A75" s="24"/>
+      <c r="A75" s="21"/>
       <c r="B75" s="3">
         <v>9</v>
       </c>
@@ -2011,7 +2274,7 @@
       <c r="D75" s="2"/>
     </row>
     <row r="76" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A76" s="24"/>
+      <c r="A76" s="21"/>
       <c r="B76" s="3">
         <v>10</v>
       </c>
@@ -2019,7 +2282,7 @@
       <c r="D76" s="2"/>
     </row>
     <row r="77" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A77" s="24"/>
+      <c r="A77" s="21"/>
       <c r="B77" s="3">
         <v>11</v>
       </c>
@@ -2027,7 +2290,7 @@
       <c r="D77" s="2"/>
     </row>
     <row r="78" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A78" s="24"/>
+      <c r="A78" s="21"/>
       <c r="B78" s="3">
         <v>12</v>
       </c>
@@ -2035,7 +2298,7 @@
       <c r="D78" s="2"/>
     </row>
     <row r="79" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A79" s="24"/>
+      <c r="A79" s="21"/>
       <c r="B79" s="3">
         <v>13</v>
       </c>
@@ -2043,7 +2306,7 @@
       <c r="D79" s="2"/>
     </row>
     <row r="80" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A80" s="24"/>
+      <c r="A80" s="21"/>
       <c r="B80" s="3">
         <v>14</v>
       </c>
@@ -2051,7 +2314,7 @@
       <c r="D80" s="2"/>
     </row>
     <row r="81" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A81" s="24"/>
+      <c r="A81" s="21"/>
       <c r="B81" s="3">
         <v>15</v>
       </c>
@@ -2059,7 +2322,7 @@
       <c r="D81" s="2"/>
     </row>
     <row r="82" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A82" s="24" t="s">
+      <c r="A82" s="21" t="s">
         <v>10</v>
       </c>
       <c r="B82" s="2">
@@ -2068,20 +2331,25 @@
       <c r="C82" s="6" t="s">
         <v>11</v>
       </c>
-      <c r="D82" s="23"/>
+      <c r="D82" s="20"/>
     </row>
     <row r="83" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A83" s="24"/>
+      <c r="A83" s="21"/>
       <c r="B83" s="2">
         <v>1</v>
       </c>
       <c r="C83" s="6" t="s">
         <v>12</v>
       </c>
-      <c r="D83" s="23"/>
+      <c r="D83" s="20"/>
     </row>
   </sheetData>
-  <mergeCells count="6">
+  <mergeCells count="11">
+    <mergeCell ref="F1:F2"/>
+    <mergeCell ref="G1:G2"/>
+    <mergeCell ref="L1:P1"/>
+    <mergeCell ref="Q1:Q2"/>
+    <mergeCell ref="H1:K1"/>
     <mergeCell ref="A2:A17"/>
     <mergeCell ref="A66:A81"/>
     <mergeCell ref="A82:A83"/>
@@ -2091,5 +2359,6 @@
   </mergeCells>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
 </worksheet>
 </file>
--- a/OV_F407VGT6_2026.01.18/天空星引脚配置.xlsx
+++ b/OV_F407VGT6_2026.01.18/天空星引脚配置.xlsx
@@ -5,10 +5,10 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="G:\Oscillatory_Viscometer\OV_F407VGT6_2026.01.18\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="G:\振动式粘度计\01_Project_Management\OV_F407VGT6_2026.01.18\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{21628AEF-5724-4F8A-B286-D625F9143E5E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{03C3FB99-5AF1-48B6-AF5E-1B5EBD086EF0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="97" uniqueCount="81">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="116" uniqueCount="98">
   <si>
     <t>A</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -359,6 +359,74 @@
   </si>
   <si>
     <t>F407VGT6</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>提高占空比</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>调整（提升）振动强度的方式</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>型号</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>V1.0</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>V2.0-A</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>V2.0-B</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>V2.0-C</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>特征</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>磁吸驱动</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>LDC_INT</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>降低高频PWM频率</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>仿真频率</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>测量频率</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>采样率</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>6.045kSPS（0x00A2）</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>3.008kSPS（0x0149）</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>斥力驱动</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -368,9 +436,9 @@
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <numFmts count="2">
     <numFmt numFmtId="176" formatCode="[&gt;=1000000]0.##,,&quot;M&quot;;[&gt;=1000]0.##,&quot;k&quot;;0"/>
-    <numFmt numFmtId="180" formatCode="0_);[Red]\(0\)"/>
+    <numFmt numFmtId="177" formatCode="0_);[Red]\(0\)"/>
   </numFmts>
-  <fonts count="5" x14ac:knownFonts="1">
+  <fonts count="7" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -402,6 +470,24 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <sz val="11"/>
+      <color theme="0"/>
+      <name val="等线"/>
+      <family val="3"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="12"/>
+      <color theme="1"/>
+      <name val="等线"/>
+      <family val="3"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
       <sz val="11"/>
       <color theme="0"/>
       <name val="等线"/>
@@ -634,7 +720,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="45">
+  <cellXfs count="47">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -696,49 +782,61 @@
     <xf numFmtId="0" fontId="0" fillId="4" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="177" fontId="0" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="177" fontId="0" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="177" fontId="0" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="10" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="7" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="6" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="7" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="7" borderId="10" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="7" borderId="11" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="4" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="6" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="12" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="180" fontId="0" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="180" fontId="0" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="180" fontId="0" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="6" borderId="10" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="7" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="6" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="7" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="176" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="7" borderId="10" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="7" borderId="11" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="6" borderId="4" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="6" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="12" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="11" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="3" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -747,25 +845,19 @@
     <xf numFmtId="0" fontId="3" fillId="3" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="12" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="9" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="9" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="9" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="8" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="8" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="8" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="9" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="9" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="8" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="8" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="8" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -1056,11 +1148,11 @@
     <col min="3" max="3" width="14.375" style="1" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="14.75" style="1" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="13.625" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="6.75" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="5.75" style="1" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="9.25" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="27.625" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="8" width="9.75" style="1" bestFit="1" customWidth="1"/>
     <col min="9" max="9" width="15" style="1" bestFit="1" customWidth="1"/>
-    <col min="10" max="11" width="8.625" style="1" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="22.75" style="1" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="8.625" style="1" bestFit="1" customWidth="1"/>
     <col min="12" max="12" width="6.125" style="1" bestFit="1" customWidth="1"/>
     <col min="13" max="13" width="9.25" style="1" bestFit="1" customWidth="1"/>
     <col min="14" max="14" width="15" style="1" bestFit="1" customWidth="1"/>
@@ -1082,31 +1174,31 @@
       <c r="D1" s="5" t="s">
         <v>9</v>
       </c>
-      <c r="F1" s="36" t="s">
+      <c r="F1" s="40" t="s">
         <v>55</v>
       </c>
-      <c r="G1" s="36" t="s">
+      <c r="G1" s="40" t="s">
         <v>65</v>
       </c>
-      <c r="H1" s="42" t="s">
+      <c r="H1" s="44" t="s">
         <v>79</v>
       </c>
-      <c r="I1" s="43"/>
-      <c r="J1" s="43"/>
-      <c r="K1" s="44"/>
-      <c r="L1" s="39" t="s">
+      <c r="I1" s="45"/>
+      <c r="J1" s="45"/>
+      <c r="K1" s="46"/>
+      <c r="L1" s="42" t="s">
         <v>80</v>
       </c>
-      <c r="M1" s="40"/>
-      <c r="N1" s="40"/>
-      <c r="O1" s="40"/>
-      <c r="P1" s="41"/>
-      <c r="Q1" s="36" t="s">
+      <c r="M1" s="42"/>
+      <c r="N1" s="42"/>
+      <c r="O1" s="42"/>
+      <c r="P1" s="43"/>
+      <c r="Q1" s="40" t="s">
         <v>57</v>
       </c>
     </row>
     <row r="2" spans="1:17" x14ac:dyDescent="0.2">
-      <c r="A2" s="21" t="s">
+      <c r="A2" s="35" t="s">
         <v>0</v>
       </c>
       <c r="B2" s="3">
@@ -1117,12 +1209,12 @@
       </c>
       <c r="D2" s="20"/>
       <c r="E2" s="18"/>
-      <c r="F2" s="37"/>
-      <c r="G2" s="37"/>
-      <c r="H2" s="23" t="s">
+      <c r="F2" s="41"/>
+      <c r="G2" s="41"/>
+      <c r="H2" s="21" t="s">
         <v>53</v>
       </c>
-      <c r="I2" s="23" t="s">
+      <c r="I2" s="21" t="s">
         <v>54</v>
       </c>
       <c r="J2" s="9" t="s">
@@ -1131,10 +1223,10 @@
       <c r="K2" s="5" t="s">
         <v>56</v>
       </c>
-      <c r="L2" s="23" t="s">
+      <c r="L2" s="21" t="s">
         <v>64</v>
       </c>
-      <c r="M2" s="23" t="s">
+      <c r="M2" s="21" t="s">
         <v>53</v>
       </c>
       <c r="N2" s="5" t="s">
@@ -1146,10 +1238,10 @@
       <c r="P2" s="5" t="s">
         <v>56</v>
       </c>
-      <c r="Q2" s="37"/>
+      <c r="Q2" s="41"/>
     </row>
     <row r="3" spans="1:17" x14ac:dyDescent="0.2">
-      <c r="A3" s="21"/>
+      <c r="A3" s="35"/>
       <c r="B3" s="3">
         <v>1</v>
       </c>
@@ -1158,16 +1250,15 @@
         <v>48</v>
       </c>
       <c r="E3" s="18"/>
-      <c r="F3" s="35" t="s">
+      <c r="F3" s="32" t="s">
         <v>49</v>
       </c>
-      <c r="G3" s="34" t="s">
+      <c r="G3" s="31" t="s">
         <v>66</v>
       </c>
-      <c r="H3" s="22"/>
       <c r="I3" s="10"/>
       <c r="J3" s="11" t="e">
-        <f>$J$2/(H3*I3)</f>
+        <f t="shared" ref="J3:J15" si="0">$J$2/(H3*I3)</f>
         <v>#VALUE!</v>
       </c>
       <c r="K3" s="10" t="e">
@@ -1178,7 +1269,7 @@
            TEXT(_xlpm.t,"0.###")&amp;" s"))))</f>
         <v>#VALUE!</v>
       </c>
-      <c r="L3" s="25">
+      <c r="L3" s="23">
         <v>168</v>
       </c>
       <c r="M3" s="10">
@@ -1187,7 +1278,7 @@
       <c r="N3" s="11">
         <v>10</v>
       </c>
-      <c r="O3" s="31">
+      <c r="O3" s="13">
         <f>L3*1000000/(M3*N3)</f>
         <v>100000</v>
       </c>
@@ -1199,12 +1290,12 @@
            TEXT(_xlpm.t,"0.###")&amp;" s"))))</f>
         <v>10. µs</v>
       </c>
-      <c r="Q3" s="38" t="s">
+      <c r="Q3" s="33" t="s">
         <v>58</v>
       </c>
     </row>
     <row r="4" spans="1:17" x14ac:dyDescent="0.2">
-      <c r="A4" s="21"/>
+      <c r="A4" s="35"/>
       <c r="B4" s="3">
         <v>2</v>
       </c>
@@ -1213,101 +1304,99 @@
         <v>43</v>
       </c>
       <c r="E4" s="18"/>
-      <c r="F4" s="28" t="s">
+      <c r="F4" s="26" t="s">
         <v>50</v>
       </c>
-      <c r="G4" s="32" t="s">
+      <c r="G4" s="29" t="s">
         <v>67</v>
       </c>
-      <c r="H4" s="22"/>
       <c r="J4" s="13" t="e">
-        <f>$J$2/(H4*I4)</f>
-        <v>#VALUE!</v>
-      </c>
-      <c r="K4" s="22" t="e">
-        <f t="shared" ref="K4:K16" si="0">_xlfn.LET(_xlpm.t,1/J4,
+        <f t="shared" si="0"/>
+        <v>#VALUE!</v>
+      </c>
+      <c r="K4" s="1" t="e">
+        <f t="shared" ref="K4:K16" si="1">_xlfn.LET(_xlpm.t,1/J4,
  IF(_xlpm.t&lt;0.000001, TEXT(_xlpm.t*1000000000,"0.###")&amp;" ns",
  IF(_xlpm.t&lt;0.001, TEXT(_xlpm.t*1000000,"0.###")&amp;" µs",
  IF(_xlpm.t&lt;1,    TEXT(_xlpm.t*1000,"0.###")&amp;" ms",
            TEXT(_xlpm.t,"0.###")&amp;" s"))))</f>
         <v>#VALUE!</v>
       </c>
-      <c r="L4" s="24">
+      <c r="L4" s="22">
         <v>84</v>
       </c>
-      <c r="M4" s="22">
-        <v>336</v>
+      <c r="M4" s="1">
+        <v>2688</v>
       </c>
       <c r="N4" s="13">
         <v>50</v>
       </c>
-      <c r="O4" s="31">
-        <f t="shared" ref="O4:O16" si="1">L4*1000000/(M4*N4)</f>
+      <c r="O4" s="13">
+        <f t="shared" ref="O4:O16" si="2">L4*1000000/(M4*N4)</f>
+        <v>625</v>
+      </c>
+      <c r="P4" s="14" t="str">
+        <f t="shared" ref="P4:P16" si="3">_xlfn.LET(_xlpm.t,1/O4,
+ IF(_xlpm.t&lt;0.000001, TEXT(_xlpm.t*1000000000,"0.###")&amp;" ns",
+ IF(_xlpm.t&lt;0.001, TEXT(_xlpm.t*1000000,"0.###")&amp;" µs",
+ IF(_xlpm.t&lt;1,    TEXT(_xlpm.t*1000,"0.###")&amp;" ms",
+           TEXT(_xlpm.t,"0.###")&amp;" s"))))</f>
+        <v>1.6 ms</v>
+      </c>
+      <c r="Q4" s="18" t="s">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="5" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="A5" s="35"/>
+      <c r="B5" s="3">
+        <v>3</v>
+      </c>
+      <c r="C5" s="20"/>
+      <c r="D5" s="8" t="s">
+        <v>44</v>
+      </c>
+      <c r="F5" s="26" t="s">
+        <v>51</v>
+      </c>
+      <c r="G5" s="29" t="s">
+        <v>67</v>
+      </c>
+      <c r="J5" s="13" t="e">
+        <f t="shared" si="0"/>
+        <v>#VALUE!</v>
+      </c>
+      <c r="K5" s="1" t="e">
+        <f t="shared" si="1"/>
+        <v>#VALUE!</v>
+      </c>
+      <c r="L5" s="22">
+        <v>84</v>
+      </c>
+      <c r="M5" s="1">
+        <v>336</v>
+      </c>
+      <c r="N5" s="13">
+        <v>50</v>
+      </c>
+      <c r="O5" s="13">
+        <f t="shared" si="2"/>
         <v>5000</v>
       </c>
-      <c r="P4" s="14" t="str">
-        <f t="shared" ref="P4:P16" si="2">_xlfn.LET(_xlpm.t,1/O4,
+      <c r="P5" s="14" t="str">
+        <f t="shared" ref="P5" si="4">_xlfn.LET(_xlpm.t,1/O5,
  IF(_xlpm.t&lt;0.000001, TEXT(_xlpm.t*1000000000,"0.###")&amp;" ns",
  IF(_xlpm.t&lt;0.001, TEXT(_xlpm.t*1000000,"0.###")&amp;" µs",
  IF(_xlpm.t&lt;1,    TEXT(_xlpm.t*1000,"0.###")&amp;" ms",
            TEXT(_xlpm.t,"0.###")&amp;" s"))))</f>
         <v>200. µs</v>
       </c>
-      <c r="Q4" s="18" t="s">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="5" spans="1:17" x14ac:dyDescent="0.2">
-      <c r="A5" s="21"/>
-      <c r="B5" s="3">
-        <v>3</v>
-      </c>
-      <c r="C5" s="20"/>
-      <c r="D5" s="8" t="s">
-        <v>44</v>
-      </c>
-      <c r="F5" s="28" t="s">
-        <v>51</v>
-      </c>
-      <c r="G5" s="32" t="s">
-        <v>67</v>
-      </c>
-      <c r="H5" s="22"/>
-      <c r="J5" s="13" t="e">
-        <f>$J$2/(H5*I5)</f>
-        <v>#VALUE!</v>
-      </c>
-      <c r="K5" s="22" t="e">
-        <f t="shared" si="0"/>
-        <v>#VALUE!</v>
-      </c>
-      <c r="L5" s="24">
-        <v>84</v>
-      </c>
-      <c r="M5" s="22">
-        <v>336</v>
-      </c>
-      <c r="N5" s="13">
-        <v>50</v>
-      </c>
-      <c r="O5" s="31">
-        <f t="shared" si="1"/>
-        <v>5000</v>
-      </c>
-      <c r="P5" s="14" t="str">
-        <f t="shared" ref="P5" si="3">_xlfn.LET(_xlpm.t,1/O5,
- IF(_xlpm.t&lt;0.000001, TEXT(_xlpm.t*1000000000,"0.###")&amp;" ns",
- IF(_xlpm.t&lt;0.001, TEXT(_xlpm.t*1000000,"0.###")&amp;" µs",
- IF(_xlpm.t&lt;1,    TEXT(_xlpm.t*1000,"0.###")&amp;" ms",
-           TEXT(_xlpm.t,"0.###")&amp;" s"))))</f>
-        <v>200. µs</v>
-      </c>
       <c r="Q5" s="18" t="s">
         <v>61</v>
       </c>
     </row>
     <row r="6" spans="1:17" x14ac:dyDescent="0.2">
-      <c r="A6" s="21"/>
+      <c r="A6" s="35"/>
       <c r="B6" s="3">
         <v>4</v>
       </c>
@@ -1317,36 +1406,35 @@
       <c r="D6" s="2" t="s">
         <v>45</v>
       </c>
-      <c r="F6" s="28" t="s">
+      <c r="F6" s="26" t="s">
         <v>52</v>
       </c>
-      <c r="G6" s="32" t="s">
+      <c r="G6" s="29" t="s">
         <v>67</v>
       </c>
-      <c r="H6" s="22"/>
       <c r="J6" s="13" t="e">
-        <f>$J$2/(H6*I6)</f>
-        <v>#VALUE!</v>
-      </c>
-      <c r="K6" s="22" t="e">
         <f t="shared" si="0"/>
         <v>#VALUE!</v>
       </c>
-      <c r="L6" s="24">
+      <c r="K6" s="1" t="e">
+        <f t="shared" si="1"/>
+        <v>#VALUE!</v>
+      </c>
+      <c r="L6" s="22">
         <v>84</v>
       </c>
-      <c r="M6" s="22">
+      <c r="M6" s="1">
         <v>8400</v>
       </c>
       <c r="N6" s="13">
         <v>10</v>
       </c>
-      <c r="O6" s="31">
-        <f t="shared" si="1"/>
+      <c r="O6" s="13">
+        <f t="shared" si="2"/>
         <v>1000</v>
       </c>
       <c r="P6" s="14" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>1. ms</v>
       </c>
       <c r="Q6" s="18" t="s">
@@ -1354,7 +1442,7 @@
       </c>
     </row>
     <row r="7" spans="1:17" x14ac:dyDescent="0.2">
-      <c r="A7" s="21"/>
+      <c r="A7" s="35"/>
       <c r="B7" s="3">
         <v>5</v>
       </c>
@@ -1364,36 +1452,35 @@
       <c r="D7" s="2" t="s">
         <v>47</v>
       </c>
-      <c r="F7" s="28" t="s">
+      <c r="F7" s="26" t="s">
         <v>73</v>
       </c>
-      <c r="G7" s="32" t="s">
+      <c r="G7" s="29" t="s">
         <v>67</v>
       </c>
-      <c r="H7" s="22"/>
       <c r="J7" s="13" t="e">
-        <f>$J$2/(H7*I7)</f>
-        <v>#VALUE!</v>
-      </c>
-      <c r="K7" s="22" t="e">
         <f t="shared" si="0"/>
         <v>#VALUE!</v>
       </c>
-      <c r="L7" s="24">
+      <c r="K7" s="1" t="e">
+        <f t="shared" si="1"/>
+        <v>#VALUE!</v>
+      </c>
+      <c r="L7" s="22">
         <v>84</v>
       </c>
-      <c r="M7" s="22">
+      <c r="M7" s="1">
         <v>84</v>
       </c>
       <c r="N7" s="13">
         <v>25</v>
       </c>
-      <c r="O7" s="31">
-        <f t="shared" si="1"/>
+      <c r="O7" s="13">
+        <f t="shared" si="2"/>
         <v>40000</v>
       </c>
       <c r="P7" s="14" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>25. µs</v>
       </c>
       <c r="Q7" s="18" t="s">
@@ -1401,7 +1488,7 @@
       </c>
     </row>
     <row r="8" spans="1:17" x14ac:dyDescent="0.2">
-      <c r="A8" s="21"/>
+      <c r="A8" s="35"/>
       <c r="B8" s="3">
         <v>6</v>
       </c>
@@ -1411,38 +1498,36 @@
       <c r="D8" s="2" t="s">
         <v>63</v>
       </c>
-      <c r="F8" s="28" t="s">
+      <c r="F8" s="26" t="s">
         <v>74</v>
       </c>
-      <c r="G8" s="32" t="s">
+      <c r="G8" s="29" t="s">
         <v>67</v>
       </c>
-      <c r="H8" s="22"/>
       <c r="J8" s="13" t="e">
-        <f>$J$2/(H8*I8)</f>
-        <v>#VALUE!</v>
-      </c>
-      <c r="K8" s="22" t="e">
         <f t="shared" si="0"/>
         <v>#VALUE!</v>
       </c>
-      <c r="L8" s="24">
+      <c r="K8" s="1" t="e">
+        <f t="shared" si="1"/>
+        <v>#VALUE!</v>
+      </c>
+      <c r="L8" s="22">
         <v>84</v>
       </c>
-      <c r="M8" s="22"/>
       <c r="N8" s="13"/>
-      <c r="O8" s="31" t="e">
-        <f t="shared" si="1"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="P8" s="14" t="e">
+      <c r="O8" s="13" t="e">
         <f t="shared" si="2"/>
         <v>#DIV/0!</v>
       </c>
+      <c r="P8" s="14" t="e">
+        <f t="shared" si="3"/>
+        <v>#DIV/0!</v>
+      </c>
       <c r="Q8" s="18"/>
     </row>
     <row r="9" spans="1:17" x14ac:dyDescent="0.2">
-      <c r="A9" s="21"/>
+      <c r="A9" s="35"/>
       <c r="B9" s="3">
         <v>7</v>
       </c>
@@ -1450,75 +1535,71 @@
         <v>25</v>
       </c>
       <c r="D9" s="2"/>
-      <c r="F9" s="28" t="s">
+      <c r="F9" s="26" t="s">
         <v>75</v>
       </c>
-      <c r="G9" s="32" t="s">
+      <c r="G9" s="29" t="s">
         <v>67</v>
       </c>
-      <c r="H9" s="22"/>
       <c r="J9" s="13" t="e">
-        <f>$J$2/(H9*I9)</f>
-        <v>#VALUE!</v>
-      </c>
-      <c r="K9" s="22" t="e">
         <f t="shared" si="0"/>
         <v>#VALUE!</v>
       </c>
-      <c r="L9" s="24">
+      <c r="K9" s="1" t="e">
+        <f t="shared" si="1"/>
+        <v>#VALUE!</v>
+      </c>
+      <c r="L9" s="22">
         <v>84</v>
       </c>
-      <c r="M9" s="22"/>
       <c r="N9" s="13"/>
-      <c r="O9" s="31" t="e">
-        <f t="shared" si="1"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="P9" s="14" t="e">
+      <c r="O9" s="13" t="e">
         <f t="shared" si="2"/>
         <v>#DIV/0!</v>
       </c>
+      <c r="P9" s="14" t="e">
+        <f t="shared" si="3"/>
+        <v>#DIV/0!</v>
+      </c>
       <c r="Q9" s="18"/>
     </row>
     <row r="10" spans="1:17" x14ac:dyDescent="0.2">
-      <c r="A10" s="21"/>
+      <c r="A10" s="35"/>
       <c r="B10" s="3">
         <v>8</v>
       </c>
       <c r="C10" s="2"/>
       <c r="D10" s="2"/>
-      <c r="F10" s="29" t="s">
+      <c r="F10" s="27" t="s">
         <v>69</v>
       </c>
-      <c r="G10" s="27" t="s">
+      <c r="G10" s="25" t="s">
         <v>66</v>
       </c>
-      <c r="H10" s="22"/>
       <c r="J10" s="13" t="e">
-        <f>$J$2/(H10*I10)</f>
-        <v>#VALUE!</v>
-      </c>
-      <c r="K10" s="22" t="e">
         <f t="shared" si="0"/>
         <v>#VALUE!</v>
       </c>
-      <c r="L10" s="24">
+      <c r="K10" s="1" t="e">
+        <f t="shared" si="1"/>
+        <v>#VALUE!</v>
+      </c>
+      <c r="L10" s="22">
         <v>168</v>
       </c>
-      <c r="M10" s="22"/>
       <c r="N10" s="13"/>
-      <c r="O10" s="31" t="e">
-        <f t="shared" si="1"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="P10" s="14" t="e">
+      <c r="O10" s="13" t="e">
         <f t="shared" si="2"/>
         <v>#DIV/0!</v>
       </c>
+      <c r="P10" s="14" t="e">
+        <f t="shared" si="3"/>
+        <v>#DIV/0!</v>
+      </c>
       <c r="Q10" s="18"/>
     </row>
     <row r="11" spans="1:17" x14ac:dyDescent="0.2">
-      <c r="A11" s="21"/>
+      <c r="A11" s="35"/>
       <c r="B11" s="2">
         <v>9</v>
       </c>
@@ -1526,37 +1607,35 @@
         <v>15</v>
       </c>
       <c r="D11" s="2"/>
-      <c r="F11" s="29" t="s">
+      <c r="F11" s="27" t="s">
         <v>70</v>
       </c>
-      <c r="G11" s="27" t="s">
+      <c r="G11" s="25" t="s">
         <v>66</v>
       </c>
-      <c r="H11" s="22"/>
       <c r="J11" s="13" t="e">
-        <f>$J$2/(H11*I11)</f>
-        <v>#VALUE!</v>
-      </c>
-      <c r="K11" s="22" t="e">
         <f t="shared" si="0"/>
         <v>#VALUE!</v>
       </c>
-      <c r="L11" s="24">
+      <c r="K11" s="1" t="e">
+        <f t="shared" si="1"/>
+        <v>#VALUE!</v>
+      </c>
+      <c r="L11" s="22">
         <v>168</v>
       </c>
-      <c r="M11" s="22"/>
-      <c r="O11" s="31" t="e">
-        <f t="shared" si="1"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="P11" s="14" t="e">
+      <c r="O11" s="13" t="e">
         <f t="shared" si="2"/>
         <v>#DIV/0!</v>
       </c>
+      <c r="P11" s="14" t="e">
+        <f t="shared" si="3"/>
+        <v>#DIV/0!</v>
+      </c>
       <c r="Q11" s="18"/>
     </row>
     <row r="12" spans="1:17" x14ac:dyDescent="0.2">
-      <c r="A12" s="21"/>
+      <c r="A12" s="35"/>
       <c r="B12" s="2">
         <v>10</v>
       </c>
@@ -1564,38 +1643,36 @@
         <v>16</v>
       </c>
       <c r="D12" s="2"/>
-      <c r="F12" s="29" t="s">
+      <c r="F12" s="27" t="s">
         <v>71</v>
       </c>
-      <c r="G12" s="27" t="s">
+      <c r="G12" s="25" t="s">
         <v>66</v>
       </c>
-      <c r="H12" s="22"/>
       <c r="J12" s="13" t="e">
-        <f>$J$2/(H12*I12)</f>
-        <v>#VALUE!</v>
-      </c>
-      <c r="K12" s="22" t="e">
         <f t="shared" si="0"/>
         <v>#VALUE!</v>
       </c>
-      <c r="L12" s="24">
+      <c r="K12" s="1" t="e">
+        <f t="shared" si="1"/>
+        <v>#VALUE!</v>
+      </c>
+      <c r="L12" s="22">
         <v>168</v>
       </c>
-      <c r="M12" s="22"/>
       <c r="N12" s="13"/>
-      <c r="O12" s="31" t="e">
-        <f t="shared" si="1"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="P12" s="14" t="e">
+      <c r="O12" s="13" t="e">
         <f t="shared" si="2"/>
         <v>#DIV/0!</v>
       </c>
+      <c r="P12" s="14" t="e">
+        <f t="shared" si="3"/>
+        <v>#DIV/0!</v>
+      </c>
       <c r="Q12" s="18"/>
     </row>
     <row r="13" spans="1:17" x14ac:dyDescent="0.2">
-      <c r="A13" s="21"/>
+      <c r="A13" s="35"/>
       <c r="B13" s="2">
         <v>11</v>
       </c>
@@ -1603,38 +1680,36 @@
         <v>17</v>
       </c>
       <c r="D13" s="2"/>
-      <c r="F13" s="29" t="s">
+      <c r="F13" s="27" t="s">
         <v>72</v>
       </c>
-      <c r="G13" s="27" t="s">
+      <c r="G13" s="25" t="s">
         <v>66</v>
       </c>
-      <c r="H13" s="22"/>
       <c r="J13" s="13" t="e">
-        <f>$J$2/(H13*I13)</f>
-        <v>#VALUE!</v>
-      </c>
-      <c r="K13" s="22" t="e">
         <f t="shared" si="0"/>
         <v>#VALUE!</v>
       </c>
-      <c r="L13" s="24">
+      <c r="K13" s="1" t="e">
+        <f t="shared" si="1"/>
+        <v>#VALUE!</v>
+      </c>
+      <c r="L13" s="22">
         <v>168</v>
       </c>
-      <c r="M13" s="22"/>
       <c r="N13" s="13"/>
-      <c r="O13" s="31" t="e">
-        <f t="shared" si="1"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="P13" s="14" t="e">
+      <c r="O13" s="13" t="e">
         <f t="shared" si="2"/>
         <v>#DIV/0!</v>
       </c>
+      <c r="P13" s="14" t="e">
+        <f t="shared" si="3"/>
+        <v>#DIV/0!</v>
+      </c>
       <c r="Q13" s="18"/>
     </row>
     <row r="14" spans="1:17" x14ac:dyDescent="0.2">
-      <c r="A14" s="21"/>
+      <c r="A14" s="35"/>
       <c r="B14" s="2">
         <v>12</v>
       </c>
@@ -1642,38 +1717,36 @@
         <v>18</v>
       </c>
       <c r="D14" s="2"/>
-      <c r="F14" s="28" t="s">
+      <c r="F14" s="26" t="s">
         <v>76</v>
       </c>
-      <c r="G14" s="32" t="s">
+      <c r="G14" s="29" t="s">
         <v>67</v>
       </c>
-      <c r="H14" s="22"/>
       <c r="J14" s="13" t="e">
-        <f>$J$2/(H14*I14)</f>
-        <v>#VALUE!</v>
-      </c>
-      <c r="K14" s="22" t="e">
         <f t="shared" si="0"/>
         <v>#VALUE!</v>
       </c>
-      <c r="L14" s="24">
+      <c r="K14" s="1" t="e">
+        <f t="shared" si="1"/>
+        <v>#VALUE!</v>
+      </c>
+      <c r="L14" s="22">
         <v>84</v>
       </c>
-      <c r="M14" s="22"/>
       <c r="N14" s="13"/>
-      <c r="O14" s="31" t="e">
-        <f t="shared" si="1"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="P14" s="14" t="e">
+      <c r="O14" s="13" t="e">
         <f t="shared" si="2"/>
         <v>#DIV/0!</v>
       </c>
+      <c r="P14" s="14" t="e">
+        <f t="shared" si="3"/>
+        <v>#DIV/0!</v>
+      </c>
       <c r="Q14" s="18"/>
     </row>
     <row r="15" spans="1:17" x14ac:dyDescent="0.2">
-      <c r="A15" s="21"/>
+      <c r="A15" s="35"/>
       <c r="B15" s="2">
         <v>13</v>
       </c>
@@ -1681,38 +1754,36 @@
         <v>19</v>
       </c>
       <c r="D15" s="20"/>
-      <c r="F15" s="28" t="s">
+      <c r="F15" s="26" t="s">
         <v>77</v>
       </c>
-      <c r="G15" s="32" t="s">
+      <c r="G15" s="29" t="s">
         <v>67</v>
       </c>
-      <c r="H15" s="22"/>
       <c r="J15" s="13" t="e">
-        <f>$J$2/(H15*I15)</f>
-        <v>#VALUE!</v>
-      </c>
-      <c r="K15" s="22" t="e">
         <f t="shared" si="0"/>
         <v>#VALUE!</v>
       </c>
-      <c r="L15" s="24">
+      <c r="K15" s="1" t="e">
+        <f t="shared" si="1"/>
+        <v>#VALUE!</v>
+      </c>
+      <c r="L15" s="22">
         <v>84</v>
       </c>
-      <c r="M15" s="22"/>
       <c r="N15" s="13"/>
-      <c r="O15" s="31" t="e">
-        <f t="shared" si="1"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="P15" s="14" t="e">
+      <c r="O15" s="13" t="e">
         <f t="shared" si="2"/>
         <v>#DIV/0!</v>
       </c>
+      <c r="P15" s="14" t="e">
+        <f t="shared" si="3"/>
+        <v>#DIV/0!</v>
+      </c>
       <c r="Q15" s="18"/>
     </row>
     <row r="16" spans="1:17" x14ac:dyDescent="0.2">
-      <c r="A16" s="21"/>
+      <c r="A16" s="35"/>
       <c r="B16" s="2">
         <v>14</v>
       </c>
@@ -1720,10 +1791,10 @@
         <v>20</v>
       </c>
       <c r="D16" s="20"/>
-      <c r="F16" s="30" t="s">
+      <c r="F16" s="28" t="s">
         <v>78</v>
       </c>
-      <c r="G16" s="33" t="s">
+      <c r="G16" s="30" t="s">
         <v>67</v>
       </c>
       <c r="H16" s="16"/>
@@ -1733,34 +1804,34 @@
         <v>#VALUE!</v>
       </c>
       <c r="K16" s="15" t="e">
-        <f t="shared" si="0"/>
-        <v>#VALUE!</v>
-      </c>
-      <c r="L16" s="26">
+        <f t="shared" si="1"/>
+        <v>#VALUE!</v>
+      </c>
+      <c r="L16" s="24">
         <v>84</v>
       </c>
       <c r="M16" s="15"/>
       <c r="N16" s="16"/>
       <c r="O16" s="16" t="e">
-        <f t="shared" si="1"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="P16" s="17" t="e">
         <f t="shared" si="2"/>
         <v>#DIV/0!</v>
       </c>
+      <c r="P16" s="17" t="e">
+        <f t="shared" si="3"/>
+        <v>#DIV/0!</v>
+      </c>
       <c r="Q16" s="19"/>
     </row>
-    <row r="17" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A17" s="21"/>
+    <row r="17" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A17" s="35"/>
       <c r="B17" s="3">
         <v>15</v>
       </c>
       <c r="C17" s="2"/>
       <c r="D17" s="2"/>
     </row>
-    <row r="18" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A18" s="21" t="s">
+    <row r="18" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A18" s="35" t="s">
         <v>1</v>
       </c>
       <c r="B18" s="3">
@@ -1769,16 +1840,19 @@
       <c r="C18" s="2"/>
       <c r="D18" s="2"/>
     </row>
-    <row r="19" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A19" s="21"/>
+    <row r="19" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A19" s="35"/>
       <c r="B19" s="3">
         <v>1</v>
       </c>
       <c r="C19" s="2"/>
       <c r="D19" s="2"/>
-    </row>
-    <row r="20" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A20" s="21"/>
+      <c r="F19" s="4" t="s">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="20" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A20" s="35"/>
       <c r="B20" s="2">
         <v>2</v>
       </c>
@@ -1786,9 +1860,12 @@
         <v>46</v>
       </c>
       <c r="D20" s="20"/>
-    </row>
-    <row r="21" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A21" s="21"/>
+      <c r="F20" s="1" t="s">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="21" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A21" s="35"/>
       <c r="B21" s="2">
         <v>3</v>
       </c>
@@ -1796,25 +1873,28 @@
         <v>21</v>
       </c>
       <c r="D21" s="2"/>
-    </row>
-    <row r="22" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A22" s="21"/>
+      <c r="F21" s="1" t="s">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="22" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A22" s="35"/>
       <c r="B22" s="3">
         <v>4</v>
       </c>
       <c r="C22" s="2"/>
       <c r="D22" s="2"/>
     </row>
-    <row r="23" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A23" s="21"/>
+    <row r="23" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A23" s="35"/>
       <c r="B23" s="3">
         <v>5</v>
       </c>
       <c r="C23" s="2"/>
       <c r="D23" s="2"/>
     </row>
-    <row r="24" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A24" s="21"/>
+    <row r="24" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A24" s="35"/>
       <c r="B24" s="3">
         <v>6</v>
       </c>
@@ -1823,8 +1903,8 @@
         <v>36</v>
       </c>
     </row>
-    <row r="25" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A25" s="21"/>
+    <row r="25" spans="1:10" ht="15.75" x14ac:dyDescent="0.2">
+      <c r="A25" s="35"/>
       <c r="B25" s="3">
         <v>7</v>
       </c>
@@ -1832,25 +1912,70 @@
       <c r="D25" s="8" t="s">
         <v>37</v>
       </c>
-    </row>
-    <row r="26" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A26" s="21"/>
+      <c r="F25" s="34" t="s">
+        <v>83</v>
+      </c>
+      <c r="G25" s="34" t="s">
+        <v>92</v>
+      </c>
+      <c r="H25" s="34" t="s">
+        <v>93</v>
+      </c>
+      <c r="I25" s="34" t="s">
+        <v>88</v>
+      </c>
+      <c r="J25" s="34" t="s">
+        <v>94</v>
+      </c>
+    </row>
+    <row r="26" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A26" s="35"/>
       <c r="B26" s="3">
         <v>8</v>
       </c>
       <c r="C26" s="20"/>
       <c r="D26" s="8"/>
-    </row>
-    <row r="27" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A27" s="21"/>
+      <c r="F26" s="1" t="s">
+        <v>84</v>
+      </c>
+      <c r="G26" s="1">
+        <v>200</v>
+      </c>
+      <c r="H26" s="1">
+        <v>197</v>
+      </c>
+      <c r="I26" s="1" t="s">
+        <v>97</v>
+      </c>
+      <c r="J26" s="1" t="s">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="27" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A27" s="35"/>
       <c r="B27" s="3">
         <v>9</v>
       </c>
       <c r="C27" s="20"/>
       <c r="D27" s="8"/>
-    </row>
-    <row r="28" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A28" s="21"/>
+      <c r="F27" s="1" t="s">
+        <v>85</v>
+      </c>
+      <c r="G27" s="1">
+        <v>500</v>
+      </c>
+      <c r="H27" s="1">
+        <v>543</v>
+      </c>
+      <c r="I27" s="39" t="s">
+        <v>89</v>
+      </c>
+      <c r="J27" s="1" t="s">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="28" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A28" s="35"/>
       <c r="B28" s="3">
         <v>10</v>
       </c>
@@ -1858,9 +1983,22 @@
       <c r="D28" s="8" t="s">
         <v>41</v>
       </c>
-    </row>
-    <row r="29" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A29" s="21"/>
+      <c r="F28" s="1" t="s">
+        <v>86</v>
+      </c>
+      <c r="G28" s="1">
+        <v>1000</v>
+      </c>
+      <c r="H28" s="1">
+        <v>269</v>
+      </c>
+      <c r="I28" s="39"/>
+      <c r="J28" s="1" t="s">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="29" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A29" s="35"/>
       <c r="B29" s="3">
         <v>11</v>
       </c>
@@ -1868,9 +2006,22 @@
       <c r="D29" s="8" t="s">
         <v>42</v>
       </c>
-    </row>
-    <row r="30" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A30" s="21"/>
+      <c r="F29" s="1" t="s">
+        <v>87</v>
+      </c>
+      <c r="G29" s="1">
+        <v>254</v>
+      </c>
+      <c r="H29" s="1">
+        <v>276</v>
+      </c>
+      <c r="I29" s="39"/>
+      <c r="J29" s="1" t="s">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="30" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A30" s="35"/>
       <c r="B30" s="3">
         <v>12</v>
       </c>
@@ -1879,8 +2030,8 @@
         <v>35</v>
       </c>
     </row>
-    <row r="31" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A31" s="21"/>
+    <row r="31" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A31" s="35"/>
       <c r="B31" s="3">
         <v>13</v>
       </c>
@@ -1889,8 +2040,8 @@
         <v>38</v>
       </c>
     </row>
-    <row r="32" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A32" s="21"/>
+    <row r="32" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A32" s="35"/>
       <c r="B32" s="3">
         <v>14</v>
       </c>
@@ -1900,7 +2051,7 @@
       </c>
     </row>
     <row r="33" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A33" s="21"/>
+      <c r="A33" s="35"/>
       <c r="B33" s="3">
         <v>15</v>
       </c>
@@ -1910,7 +2061,7 @@
       </c>
     </row>
     <row r="34" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A34" s="21" t="s">
+      <c r="A34" s="36" t="s">
         <v>2</v>
       </c>
       <c r="B34" s="3">
@@ -1920,7 +2071,7 @@
       <c r="D34" s="2"/>
     </row>
     <row r="35" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A35" s="21"/>
+      <c r="A35" s="37"/>
       <c r="B35" s="3">
         <v>1</v>
       </c>
@@ -1928,7 +2079,7 @@
       <c r="D35" s="2"/>
     </row>
     <row r="36" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A36" s="21"/>
+      <c r="A36" s="37"/>
       <c r="B36" s="3">
         <v>2</v>
       </c>
@@ -1936,7 +2087,7 @@
       <c r="D36" s="2"/>
     </row>
     <row r="37" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A37" s="21"/>
+      <c r="A37" s="37"/>
       <c r="B37" s="3">
         <v>3</v>
       </c>
@@ -1944,7 +2095,7 @@
       <c r="D37" s="2"/>
     </row>
     <row r="38" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A38" s="21"/>
+      <c r="A38" s="37"/>
       <c r="B38" s="3">
         <v>4</v>
       </c>
@@ -1952,7 +2103,7 @@
       <c r="D38" s="2"/>
     </row>
     <row r="39" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A39" s="21"/>
+      <c r="A39" s="37"/>
       <c r="B39" s="3">
         <v>5</v>
       </c>
@@ -1960,7 +2111,7 @@
       <c r="D39" s="2"/>
     </row>
     <row r="40" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A40" s="21"/>
+      <c r="A40" s="37"/>
       <c r="B40" s="3">
         <v>6</v>
       </c>
@@ -1968,7 +2119,7 @@
       <c r="D40" s="2"/>
     </row>
     <row r="41" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A41" s="21"/>
+      <c r="A41" s="37"/>
       <c r="B41" s="3">
         <v>7</v>
       </c>
@@ -1976,7 +2127,7 @@
       <c r="D41" s="2"/>
     </row>
     <row r="42" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A42" s="21"/>
+      <c r="A42" s="37"/>
       <c r="B42" s="3">
         <v>8</v>
       </c>
@@ -1986,7 +2137,7 @@
       <c r="D42" s="2"/>
     </row>
     <row r="43" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A43" s="21"/>
+      <c r="A43" s="37"/>
       <c r="B43" s="3">
         <v>9</v>
       </c>
@@ -1996,7 +2147,7 @@
       <c r="D43" s="2"/>
     </row>
     <row r="44" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A44" s="21"/>
+      <c r="A44" s="37"/>
       <c r="B44" s="3">
         <v>10</v>
       </c>
@@ -2006,7 +2157,7 @@
       <c r="D44" s="2"/>
     </row>
     <row r="45" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A45" s="21"/>
+      <c r="A45" s="37"/>
       <c r="B45" s="3">
         <v>11</v>
       </c>
@@ -2016,7 +2167,7 @@
       <c r="D45" s="2"/>
     </row>
     <row r="46" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A46" s="21"/>
+      <c r="A46" s="37"/>
       <c r="B46" s="3">
         <v>12</v>
       </c>
@@ -2026,7 +2177,7 @@
       <c r="D46" s="2"/>
     </row>
     <row r="47" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A47" s="21"/>
+      <c r="A47" s="37"/>
       <c r="B47" s="3">
         <v>13</v>
       </c>
@@ -2034,7 +2185,7 @@
       <c r="D47" s="2"/>
     </row>
     <row r="48" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A48" s="21"/>
+      <c r="A48" s="37"/>
       <c r="B48" s="2">
         <v>14</v>
       </c>
@@ -2044,7 +2195,7 @@
       <c r="D48" s="8"/>
     </row>
     <row r="49" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A49" s="21"/>
+      <c r="A49" s="38"/>
       <c r="B49" s="2">
         <v>15</v>
       </c>
@@ -2054,7 +2205,7 @@
       <c r="D49" s="8"/>
     </row>
     <row r="50" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A50" s="21" t="s">
+      <c r="A50" s="35" t="s">
         <v>3</v>
       </c>
       <c r="B50" s="3">
@@ -2066,7 +2217,7 @@
       </c>
     </row>
     <row r="51" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A51" s="21"/>
+      <c r="A51" s="35"/>
       <c r="B51" s="3">
         <v>1</v>
       </c>
@@ -2076,7 +2227,7 @@
       </c>
     </row>
     <row r="52" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A52" s="21"/>
+      <c r="A52" s="35"/>
       <c r="B52" s="3">
         <v>2</v>
       </c>
@@ -2086,7 +2237,7 @@
       <c r="D52" s="2"/>
     </row>
     <row r="53" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A53" s="21"/>
+      <c r="A53" s="35"/>
       <c r="B53" s="3">
         <v>3</v>
       </c>
@@ -2096,7 +2247,7 @@
       <c r="D53" s="2"/>
     </row>
     <row r="54" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A54" s="21"/>
+      <c r="A54" s="35"/>
       <c r="B54" s="3">
         <v>4</v>
       </c>
@@ -2104,7 +2255,7 @@
       <c r="D54" s="2"/>
     </row>
     <row r="55" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A55" s="21"/>
+      <c r="A55" s="35"/>
       <c r="B55" s="3">
         <v>5</v>
       </c>
@@ -2112,7 +2263,7 @@
       <c r="D55" s="2"/>
     </row>
     <row r="56" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A56" s="21"/>
+      <c r="A56" s="35"/>
       <c r="B56" s="3">
         <v>6</v>
       </c>
@@ -2120,7 +2271,7 @@
       <c r="D56" s="2"/>
     </row>
     <row r="57" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A57" s="21"/>
+      <c r="A57" s="35"/>
       <c r="B57" s="3">
         <v>7</v>
       </c>
@@ -2128,15 +2279,17 @@
       <c r="D57" s="2"/>
     </row>
     <row r="58" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A58" s="21"/>
+      <c r="A58" s="35"/>
       <c r="B58" s="3">
         <v>8</v>
       </c>
-      <c r="C58" s="2"/>
-      <c r="D58" s="2"/>
+      <c r="C58" s="8"/>
+      <c r="D58" s="8" t="s">
+        <v>90</v>
+      </c>
     </row>
     <row r="59" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A59" s="21"/>
+      <c r="A59" s="35"/>
       <c r="B59" s="3">
         <v>9</v>
       </c>
@@ -2144,7 +2297,7 @@
       <c r="D59" s="2"/>
     </row>
     <row r="60" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A60" s="21"/>
+      <c r="A60" s="35"/>
       <c r="B60" s="3">
         <v>10</v>
       </c>
@@ -2152,7 +2305,7 @@
       <c r="D60" s="2"/>
     </row>
     <row r="61" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A61" s="21"/>
+      <c r="A61" s="35"/>
       <c r="B61" s="3">
         <v>11</v>
       </c>
@@ -2160,7 +2313,7 @@
       <c r="D61" s="2"/>
     </row>
     <row r="62" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A62" s="21"/>
+      <c r="A62" s="35"/>
       <c r="B62" s="3">
         <v>12</v>
       </c>
@@ -2168,7 +2321,7 @@
       <c r="D62" s="2"/>
     </row>
     <row r="63" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A63" s="21"/>
+      <c r="A63" s="35"/>
       <c r="B63" s="3">
         <v>13</v>
       </c>
@@ -2176,7 +2329,7 @@
       <c r="D63" s="2"/>
     </row>
     <row r="64" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A64" s="21"/>
+      <c r="A64" s="35"/>
       <c r="B64" s="3">
         <v>14</v>
       </c>
@@ -2184,7 +2337,7 @@
       <c r="D64" s="2"/>
     </row>
     <row r="65" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A65" s="21"/>
+      <c r="A65" s="35"/>
       <c r="B65" s="3">
         <v>15</v>
       </c>
@@ -2192,7 +2345,7 @@
       <c r="D65" s="2"/>
     </row>
     <row r="66" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A66" s="21" t="s">
+      <c r="A66" s="35" t="s">
         <v>8</v>
       </c>
       <c r="B66" s="3">
@@ -2202,7 +2355,7 @@
       <c r="D66" s="2"/>
     </row>
     <row r="67" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A67" s="21"/>
+      <c r="A67" s="35"/>
       <c r="B67" s="3">
         <v>1</v>
       </c>
@@ -2210,7 +2363,7 @@
       <c r="D67" s="2"/>
     </row>
     <row r="68" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A68" s="21"/>
+      <c r="A68" s="35"/>
       <c r="B68" s="3">
         <v>2</v>
       </c>
@@ -2218,7 +2371,7 @@
       <c r="D68" s="2"/>
     </row>
     <row r="69" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A69" s="21"/>
+      <c r="A69" s="35"/>
       <c r="B69" s="3">
         <v>3</v>
       </c>
@@ -2226,7 +2379,7 @@
       <c r="D69" s="2"/>
     </row>
     <row r="70" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A70" s="21"/>
+      <c r="A70" s="35"/>
       <c r="B70" s="3">
         <v>4</v>
       </c>
@@ -2234,7 +2387,7 @@
       <c r="D70" s="2"/>
     </row>
     <row r="71" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A71" s="21"/>
+      <c r="A71" s="35"/>
       <c r="B71" s="3">
         <v>5</v>
       </c>
@@ -2242,7 +2395,7 @@
       <c r="D71" s="2"/>
     </row>
     <row r="72" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A72" s="21"/>
+      <c r="A72" s="35"/>
       <c r="B72" s="3">
         <v>6</v>
       </c>
@@ -2250,7 +2403,7 @@
       <c r="D72" s="2"/>
     </row>
     <row r="73" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A73" s="21"/>
+      <c r="A73" s="35"/>
       <c r="B73" s="3">
         <v>7</v>
       </c>
@@ -2258,7 +2411,7 @@
       <c r="D73" s="2"/>
     </row>
     <row r="74" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A74" s="21"/>
+      <c r="A74" s="35"/>
       <c r="B74" s="3">
         <v>8</v>
       </c>
@@ -2266,7 +2419,7 @@
       <c r="D74" s="2"/>
     </row>
     <row r="75" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A75" s="21"/>
+      <c r="A75" s="35"/>
       <c r="B75" s="3">
         <v>9</v>
       </c>
@@ -2274,7 +2427,7 @@
       <c r="D75" s="2"/>
     </row>
     <row r="76" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A76" s="21"/>
+      <c r="A76" s="35"/>
       <c r="B76" s="3">
         <v>10</v>
       </c>
@@ -2282,7 +2435,7 @@
       <c r="D76" s="2"/>
     </row>
     <row r="77" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A77" s="21"/>
+      <c r="A77" s="35"/>
       <c r="B77" s="3">
         <v>11</v>
       </c>
@@ -2290,7 +2443,7 @@
       <c r="D77" s="2"/>
     </row>
     <row r="78" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A78" s="21"/>
+      <c r="A78" s="35"/>
       <c r="B78" s="3">
         <v>12</v>
       </c>
@@ -2298,7 +2451,7 @@
       <c r="D78" s="2"/>
     </row>
     <row r="79" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A79" s="21"/>
+      <c r="A79" s="35"/>
       <c r="B79" s="3">
         <v>13</v>
       </c>
@@ -2306,7 +2459,7 @@
       <c r="D79" s="2"/>
     </row>
     <row r="80" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A80" s="21"/>
+      <c r="A80" s="35"/>
       <c r="B80" s="3">
         <v>14</v>
       </c>
@@ -2314,7 +2467,7 @@
       <c r="D80" s="2"/>
     </row>
     <row r="81" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A81" s="21"/>
+      <c r="A81" s="35"/>
       <c r="B81" s="3">
         <v>15</v>
       </c>
@@ -2322,7 +2475,7 @@
       <c r="D81" s="2"/>
     </row>
     <row r="82" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A82" s="21" t="s">
+      <c r="A82" s="35" t="s">
         <v>10</v>
       </c>
       <c r="B82" s="2">
@@ -2334,7 +2487,7 @@
       <c r="D82" s="20"/>
     </row>
     <row r="83" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A83" s="21"/>
+      <c r="A83" s="35"/>
       <c r="B83" s="2">
         <v>1</v>
       </c>
@@ -2344,7 +2497,8 @@
       <c r="D83" s="20"/>
     </row>
   </sheetData>
-  <mergeCells count="11">
+  <mergeCells count="12">
+    <mergeCell ref="I27:I29"/>
     <mergeCell ref="F1:F2"/>
     <mergeCell ref="G1:G2"/>
     <mergeCell ref="L1:P1"/>

--- a/OV_F407VGT6_2026.01.18/天空星引脚配置.xlsx
+++ b/OV_F407VGT6_2026.01.18/天空星引脚配置.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29822"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29929"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="G:\振动式粘度计\01_Project_Management\OV_F407VGT6_2026.01.18\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="G:\Oscillatory_Viscometer\01_Project_Management\OV_F407VGT6_2026.01.18\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{03C3FB99-5AF1-48B6-AF5E-1B5EBD086EF0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A11A42A3-F064-477C-BA65-A5D0D1CEF9DD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -418,15 +418,15 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>6.045kSPS（0x00A2）</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>3.008kSPS（0x0149）</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
     <t>斥力驱动</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>6.045kSPS（0x00A3）</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -1945,10 +1945,10 @@
         <v>197</v>
       </c>
       <c r="I26" s="1" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="J26" s="1" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
     </row>
     <row r="27" spans="1:10" x14ac:dyDescent="0.2">
@@ -1971,7 +1971,7 @@
         <v>89</v>
       </c>
       <c r="J27" s="1" t="s">
-        <v>95</v>
+        <v>97</v>
       </c>
     </row>
     <row r="28" spans="1:10" x14ac:dyDescent="0.2">
@@ -1990,11 +1990,11 @@
         <v>1000</v>
       </c>
       <c r="H28" s="1">
-        <v>269</v>
+        <v>1046</v>
       </c>
       <c r="I28" s="39"/>
       <c r="J28" s="1" t="s">
-        <v>95</v>
+        <v>97</v>
       </c>
     </row>
     <row r="29" spans="1:10" x14ac:dyDescent="0.2">
@@ -2017,7 +2017,7 @@
       </c>
       <c r="I29" s="39"/>
       <c r="J29" s="1" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
     </row>
     <row r="30" spans="1:10" x14ac:dyDescent="0.2">
